--- a/data/fmsForecastOutput/File1/RPT_RPT6603780586403AQ_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT6603780586403AQ_fmsForecastOutput.xlsx
@@ -1875,49 +1875,49 @@
         </is>
       </c>
       <c r="C8" s="148" t="n">
-        <v>458.4688261402947</v>
+        <v>224.0380206899177</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>486.8618228693556</v>
+        <v>234.4434878971769</v>
       </c>
       <c r="E8" s="149" t="n">
-        <v>519.8945746310865</v>
+        <v>247.3086470904072</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>547.6158175572276</v>
+        <v>257.4995536998771</v>
       </c>
       <c r="G8" s="150" t="n">
-        <v>577.7628316979045</v>
+        <v>268.9372553107419</v>
       </c>
       <c r="H8" s="148" t="n">
-        <v>454.5851368213866</v>
+        <v>222.1401946691001</v>
       </c>
       <c r="I8" s="149" t="n">
-        <v>483.7951970966897</v>
+        <v>232.9667846346743</v>
       </c>
       <c r="J8" s="149" t="n">
-        <v>517.6704726029918</v>
+        <v>246.2506640099924</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>546.3733946600989</v>
+        <v>256.9153424129493</v>
       </c>
       <c r="L8" s="150" t="n">
-        <v>577.6244182146324</v>
+        <v>268.8728265516613</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>52896290.2022814</v>
+        <v>25848606.23682228</v>
       </c>
       <c r="N8" s="152" t="n">
-        <v>60144332.71413735</v>
+        <v>28961907.62226669</v>
       </c>
       <c r="O8" s="152" t="n">
-        <v>68512652.08964364</v>
+        <v>32590783.06190964</v>
       </c>
       <c r="P8" s="152" t="n">
-        <v>77801415.02163078</v>
+        <v>36583730.78895816</v>
       </c>
       <c r="Q8" s="153" t="n">
-        <v>90267406.43371171</v>
+        <v>42017705.53318492</v>
       </c>
       <c r="S8" s="21" t="inlineStr">
         <is>
@@ -1925,49 +1925,49 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>562.5903825870338</v>
+        <v>274.9186609591051</v>
       </c>
       <c r="U8" s="149" t="n">
-        <v>597.4316323772796</v>
+        <v>287.6872843492971</v>
       </c>
       <c r="V8" s="149" t="n">
-        <v>637.9663588231032</v>
+        <v>303.4742134050748</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>671.9832947070566</v>
+        <v>315.9795479478774</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>708.976911834844</v>
+        <v>330.0148335731724</v>
       </c>
       <c r="Y8" s="148" t="n">
-        <v>557.87813995581</v>
+        <v>272.6159492982102</v>
       </c>
       <c r="Z8" s="149" t="n">
-        <v>593.7108585498023</v>
+        <v>285.895582571061</v>
       </c>
       <c r="AA8" s="149" t="n">
-        <v>635.2678908504295</v>
+        <v>302.1905791913262</v>
       </c>
       <c r="AB8" s="149" t="n">
-        <v>670.475916830582</v>
+        <v>315.2707497028218</v>
       </c>
       <c r="AC8" s="150" t="n">
-        <v>708.8089846069307</v>
+        <v>329.9366667453856</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>52896290.2022814</v>
+        <v>25848606.23682228</v>
       </c>
       <c r="AE8" s="152" t="n">
-        <v>60144332.71413735</v>
+        <v>28961907.62226669</v>
       </c>
       <c r="AF8" s="152" t="n">
-        <v>68512652.08964364</v>
+        <v>32590783.06190964</v>
       </c>
       <c r="AG8" s="152" t="n">
-        <v>77801415.02163078</v>
+        <v>36583730.78895816</v>
       </c>
       <c r="AH8" s="153" t="n">
-        <v>90267406.43371171</v>
+        <v>42017705.53318492</v>
       </c>
       <c r="AQ8" s="28" t="inlineStr">
         <is>
@@ -2022,49 +2022,49 @@
         </is>
       </c>
       <c r="C9" s="155" t="n">
-        <v>1017.459089724621</v>
+        <v>500.3155164385034</v>
       </c>
       <c r="D9" s="156" t="n">
-        <v>1070.108217761866</v>
+        <v>520.2306135590287</v>
       </c>
       <c r="E9" s="156" t="n">
-        <v>1136.405381929706</v>
+        <v>547.2020723060386</v>
       </c>
       <c r="F9" s="156" t="n">
-        <v>1186.119106531885</v>
+        <v>565.8818212151383</v>
       </c>
       <c r="G9" s="157" t="n">
-        <v>1240.56651372168</v>
+        <v>586.6519006132896</v>
       </c>
       <c r="H9" s="155" t="n">
-        <v>1008.392970668674</v>
+        <v>495.8574305229346</v>
       </c>
       <c r="I9" s="156" t="n">
-        <v>1062.512190779732</v>
+        <v>516.5378227627936</v>
       </c>
       <c r="J9" s="156" t="n">
-        <v>1130.486399462452</v>
+        <v>544.3519630725496</v>
       </c>
       <c r="K9" s="156" t="n">
-        <v>1182.363996795883</v>
+        <v>564.0903077620884</v>
       </c>
       <c r="L9" s="157" t="n">
-        <v>1239.232709843052</v>
+        <v>586.0211576649775</v>
       </c>
       <c r="M9" s="158" t="n">
-        <v>26185379.03705673</v>
+        <v>12876145.65378626</v>
       </c>
       <c r="N9" s="159" t="n">
-        <v>28339830.28143753</v>
+        <v>13777342.37599495</v>
       </c>
       <c r="O9" s="159" t="n">
-        <v>31393998.41144255</v>
+        <v>15116842.33626454</v>
       </c>
       <c r="P9" s="159" t="n">
-        <v>35040424.50268856</v>
+        <v>16717325.54052735</v>
       </c>
       <c r="Q9" s="160" t="n">
-        <v>40019909.31238885</v>
+        <v>18925027.88105373</v>
       </c>
       <c r="S9" s="32" t="inlineStr">
         <is>
@@ -2072,49 +2072,49 @@
         </is>
       </c>
       <c r="T9" s="155" t="n">
-        <v>1029.255918687301</v>
+        <v>506.1163752979957</v>
       </c>
       <c r="U9" s="156" t="n">
-        <v>1082.515481841557</v>
+        <v>526.2623760458793</v>
       </c>
       <c r="V9" s="156" t="n">
-        <v>1149.581321933861</v>
+        <v>553.546552708455</v>
       </c>
       <c r="W9" s="156" t="n">
-        <v>1199.871447407734</v>
+        <v>572.4428821220408</v>
       </c>
       <c r="X9" s="157" t="n">
-        <v>1254.95013968463</v>
+        <v>593.4537781551564</v>
       </c>
       <c r="Y9" s="155" t="n">
-        <v>1020.010807239</v>
+        <v>501.570273390311</v>
       </c>
       <c r="Z9" s="156" t="n">
-        <v>1074.769372405458</v>
+        <v>522.4966230147836</v>
       </c>
       <c r="AA9" s="156" t="n">
-        <v>1143.545299376819</v>
+        <v>550.6400863151941</v>
       </c>
       <c r="AB9" s="156" t="n">
-        <v>1196.042021740731</v>
+        <v>570.6159135160065</v>
       </c>
       <c r="AC9" s="157" t="n">
-        <v>1253.589915892153</v>
+        <v>592.810541485224</v>
       </c>
       <c r="AD9" s="158" t="n">
-        <v>26185379.03705673</v>
+        <v>12876145.65378626</v>
       </c>
       <c r="AE9" s="159" t="n">
-        <v>28339830.28143753</v>
+        <v>13777342.37599495</v>
       </c>
       <c r="AF9" s="159" t="n">
-        <v>31393998.41144255</v>
+        <v>15116842.33626454</v>
       </c>
       <c r="AG9" s="159" t="n">
-        <v>35040424.50268856</v>
+        <v>16717325.54052735</v>
       </c>
       <c r="AH9" s="160" t="n">
-        <v>40019909.31238885</v>
+        <v>18925027.88105373</v>
       </c>
       <c r="AJ9" s="39" t="n"/>
       <c r="AQ9" s="40" t="inlineStr">
@@ -2170,49 +2170,49 @@
         </is>
       </c>
       <c r="C10" s="161" t="n">
-        <v>560.4176239635415</v>
+        <v>274.4255862560512</v>
       </c>
       <c r="D10" s="162" t="n">
-        <v>589.8242254012563</v>
+        <v>284.8944282347566</v>
       </c>
       <c r="E10" s="162" t="n">
-        <v>626.737368215712</v>
+        <v>299.2808930727555</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>657.5287470822957</v>
+        <v>310.5849473407092</v>
       </c>
       <c r="G10" s="163" t="n">
-        <v>691.1959923103491</v>
+        <v>323.3113895634195</v>
       </c>
       <c r="H10" s="161" t="n">
-        <v>555.6253841739879</v>
+        <v>272.0789198460503</v>
       </c>
       <c r="I10" s="162" t="n">
-        <v>586.0257503979303</v>
+        <v>283.0597047398029</v>
       </c>
       <c r="J10" s="162" t="n">
-        <v>623.9550467796745</v>
+        <v>297.9522733248005</v>
       </c>
       <c r="K10" s="162" t="n">
-        <v>655.9353394508906</v>
+        <v>309.832298232228</v>
       </c>
       <c r="L10" s="163" t="n">
-        <v>690.9314916279106</v>
+        <v>323.1876676609041</v>
       </c>
       <c r="M10" s="164" t="n">
-        <v>79081669.2393381</v>
+        <v>38724751.89060854</v>
       </c>
       <c r="N10" s="165" t="n">
-        <v>88484162.99557489</v>
+        <v>42739249.99826165</v>
       </c>
       <c r="O10" s="165" t="n">
-        <v>99906650.50108619</v>
+        <v>47707625.39817418</v>
       </c>
       <c r="P10" s="165" t="n">
-        <v>112841839.5243193</v>
+        <v>53301056.32948551</v>
       </c>
       <c r="Q10" s="166" t="n">
-        <v>130287315.7461005</v>
+        <v>60942733.41423865</v>
       </c>
       <c r="S10" s="42" t="inlineStr">
         <is>
@@ -2220,49 +2220,49 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>661.9717179153971</v>
+        <v>324.1546464742809</v>
       </c>
       <c r="U10" s="162" t="n">
-        <v>697.5435349434621</v>
+        <v>336.9245581959192</v>
       </c>
       <c r="V10" s="162" t="n">
-        <v>741.6901225440173</v>
+        <v>354.1733643394558</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>778.3147219607389</v>
+        <v>367.6384310303313</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>818.3347258476836</v>
+        <v>382.7813533140665</v>
       </c>
       <c r="Y10" s="161" t="n">
-        <v>656.3415389942155</v>
+        <v>321.3976576054364</v>
       </c>
       <c r="Z10" s="162" t="n">
-        <v>693.0656179432398</v>
+        <v>334.7616534719006</v>
       </c>
       <c r="AA10" s="162" t="n">
-        <v>738.399297641928</v>
+        <v>352.6019229900318</v>
       </c>
       <c r="AB10" s="162" t="n">
-        <v>776.420033560413</v>
+        <v>366.743471380805</v>
       </c>
       <c r="AC10" s="163" t="n">
-        <v>818.0019644874262</v>
+        <v>382.6257020386327</v>
       </c>
       <c r="AD10" s="164" t="n">
-        <v>79081669.2393381</v>
+        <v>38724751.89060854</v>
       </c>
       <c r="AE10" s="165" t="n">
-        <v>88484162.99557489</v>
+        <v>42739249.99826165</v>
       </c>
       <c r="AF10" s="165" t="n">
-        <v>99906650.50108619</v>
+        <v>47707625.39817418</v>
       </c>
       <c r="AG10" s="165" t="n">
-        <v>112841839.5243193</v>
+        <v>53301056.32948551</v>
       </c>
       <c r="AH10" s="166" t="n">
-        <v>130287315.7461005</v>
+        <v>60942733.41423865</v>
       </c>
       <c r="AJ10" s="39" t="n"/>
       <c r="AQ10" s="40" t="inlineStr">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="C11" s="155" t="n">
-        <v>1179.407969332615</v>
+        <v>579.7402970241324</v>
       </c>
       <c r="D11" s="156" t="n">
-        <v>1230.465110090619</v>
+        <v>598.1635061800189</v>
       </c>
       <c r="E11" s="156" t="n">
-        <v>1289.970159450173</v>
+        <v>621.1549155934647</v>
       </c>
       <c r="F11" s="156" t="n">
-        <v>1328.432008956238</v>
+        <v>633.8033911196247</v>
       </c>
       <c r="G11" s="157" t="n">
-        <v>1362.829974063923</v>
+        <v>644.4859710592706</v>
       </c>
       <c r="H11" s="155" t="n">
-        <v>1174.31761983023</v>
+        <v>577.2381257575272</v>
       </c>
       <c r="I11" s="156" t="n">
-        <v>1227.323489221914</v>
+        <v>596.636276404463</v>
       </c>
       <c r="J11" s="156" t="n">
-        <v>1288.899814624647</v>
+        <v>620.6395161131856</v>
       </c>
       <c r="K11" s="156" t="n">
-        <v>1328.432008956238</v>
+        <v>633.8033911196247</v>
       </c>
       <c r="L11" s="157" t="n">
-        <v>1362.829974063923</v>
+        <v>644.4859710592706</v>
       </c>
       <c r="M11" s="158" t="n">
-        <v>10125003.71617656</v>
+        <v>4976965.405031301</v>
       </c>
       <c r="N11" s="159" t="n">
-        <v>11377823.52979894</v>
+        <v>5531078.256075735</v>
       </c>
       <c r="O11" s="159" t="n">
-        <v>12953290.64971427</v>
+        <v>6237353.710267489</v>
       </c>
       <c r="P11" s="159" t="n">
-        <v>14745983.66859445</v>
+        <v>7035402.934842755</v>
       </c>
       <c r="Q11" s="160" t="n">
-        <v>17074220.62643371</v>
+        <v>8074444.99308555</v>
       </c>
       <c r="S11" s="32" t="inlineStr">
         <is>
@@ -2368,49 +2368,49 @@
         </is>
       </c>
       <c r="T11" s="155" t="n">
-        <v>1435.183019264909</v>
+        <v>705.4670237165246</v>
       </c>
       <c r="U11" s="156" t="n">
-        <v>1497.312785498022</v>
+        <v>727.8856249371488</v>
       </c>
       <c r="V11" s="156" t="n">
-        <v>1569.722535662487</v>
+        <v>755.8631197795963</v>
       </c>
       <c r="W11" s="156" t="n">
-        <v>1616.525503537854</v>
+        <v>771.254636342779</v>
       </c>
       <c r="X11" s="157" t="n">
-        <v>1658.383263281289</v>
+        <v>784.2539188048055</v>
       </c>
       <c r="Y11" s="155" t="n">
-        <v>1428.530249017573</v>
+        <v>702.1968414729653</v>
       </c>
       <c r="Z11" s="156" t="n">
-        <v>1493.206344253717</v>
+        <v>725.8893689909439</v>
       </c>
       <c r="AA11" s="156" t="n">
-        <v>1568.323298900815</v>
+        <v>755.1893500910303</v>
       </c>
       <c r="AB11" s="156" t="n">
-        <v>1616.525503537854</v>
+        <v>771.254636342779</v>
       </c>
       <c r="AC11" s="157" t="n">
-        <v>1658.383263281289</v>
+        <v>784.2539188048055</v>
       </c>
       <c r="AD11" s="158" t="n">
-        <v>10125003.71617656</v>
+        <v>4976965.405031301</v>
       </c>
       <c r="AE11" s="159" t="n">
-        <v>11377823.52979894</v>
+        <v>5531078.256075735</v>
       </c>
       <c r="AF11" s="159" t="n">
-        <v>12953290.64971427</v>
+        <v>6237353.710267489</v>
       </c>
       <c r="AG11" s="159" t="n">
-        <v>14745983.66859445</v>
+        <v>7035402.934842755</v>
       </c>
       <c r="AH11" s="160" t="n">
-        <v>17074220.62643371</v>
+        <v>8074444.99308555</v>
       </c>
       <c r="AJ11" s="39" t="n"/>
       <c r="AQ11" s="40" t="inlineStr">
@@ -2461,49 +2461,49 @@
         </is>
       </c>
       <c r="C12" s="161" t="n">
-        <v>595.915498220019</v>
+        <v>291.9347821467172</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>627.019283128718</v>
+        <v>303.0825609575888</v>
       </c>
       <c r="E12" s="162" t="n">
-        <v>666.0405094103264</v>
+        <v>318.3551311400013</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>698.2873477899968</v>
+        <v>330.2210591916971</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>733.0545261349389</v>
+        <v>343.3280912914079</v>
       </c>
       <c r="H12" s="161" t="n">
-        <v>590.963863998143</v>
+        <v>289.5090116102042</v>
       </c>
       <c r="I12" s="162" t="n">
-        <v>623.1222483816329</v>
+        <v>301.1988497176509</v>
       </c>
       <c r="J12" s="162" t="n">
-        <v>663.2256927276853</v>
+        <v>317.0097004620225</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>696.6977376623872</v>
+        <v>329.4693303486894</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>732.7914840204845</v>
+        <v>343.204894798016</v>
       </c>
       <c r="M12" s="164" t="n">
-        <v>89206672.95551468</v>
+        <v>43701717.29563984</v>
       </c>
       <c r="N12" s="165" t="n">
-        <v>99861986.52537383</v>
+        <v>48270328.25433739</v>
       </c>
       <c r="O12" s="165" t="n">
-        <v>112859941.1508005</v>
+        <v>53944979.10844167</v>
       </c>
       <c r="P12" s="165" t="n">
-        <v>127587823.1929138</v>
+        <v>60336459.26432826</v>
       </c>
       <c r="Q12" s="166" t="n">
-        <v>147361536.3725343</v>
+        <v>69017178.40732419</v>
       </c>
       <c r="S12" s="42" t="inlineStr">
         <is>
@@ -2511,49 +2511,49 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>705.0870243725236</v>
+        <v>345.4171396271884</v>
       </c>
       <c r="U12" s="162" t="n">
-        <v>742.7448212954637</v>
+        <v>359.0208604956146</v>
       </c>
       <c r="V12" s="162" t="n">
-        <v>789.4881941159165</v>
+        <v>377.3608572153894</v>
       </c>
       <c r="W12" s="162" t="n">
-        <v>827.931627589575</v>
+        <v>391.5300196490995</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>869.3588179187898</v>
+        <v>407.1665789680563</v>
       </c>
       <c r="Y12" s="161" t="n">
-        <v>699.2417266850056</v>
+        <v>342.5535696880184</v>
       </c>
       <c r="Z12" s="162" t="n">
-        <v>738.1305502105575</v>
+        <v>356.7904584410117</v>
       </c>
       <c r="AA12" s="162" t="n">
-        <v>786.1463333456469</v>
+        <v>375.7635091431037</v>
       </c>
       <c r="AB12" s="162" t="n">
-        <v>826.0351847059256</v>
+        <v>390.6331891684712</v>
       </c>
       <c r="AC12" s="163" t="n">
-        <v>869.0267722811531</v>
+        <v>407.0110644859447</v>
       </c>
       <c r="AD12" s="164" t="n">
-        <v>89206672.95551468</v>
+        <v>43701717.29563984</v>
       </c>
       <c r="AE12" s="165" t="n">
-        <v>99861986.52537383</v>
+        <v>48270328.25433739</v>
       </c>
       <c r="AF12" s="165" t="n">
-        <v>112859941.1508005</v>
+        <v>53944979.10844167</v>
       </c>
       <c r="AG12" s="165" t="n">
-        <v>127587823.1929138</v>
+        <v>60336459.26432826</v>
       </c>
       <c r="AH12" s="166" t="n">
-        <v>147361536.3725343</v>
+        <v>69017178.40732419</v>
       </c>
       <c r="AQ12" s="40" t="inlineStr">
         <is>
@@ -2603,49 +2603,49 @@
         </is>
       </c>
       <c r="C13" s="155" t="n">
-        <v>6840.782953736923</v>
+        <v>3374.538433565778</v>
       </c>
       <c r="D13" s="156" t="n">
-        <v>6946.161324646021</v>
+        <v>3392.198255960482</v>
       </c>
       <c r="E13" s="156" t="n">
-        <v>7311.858462984307</v>
+        <v>3617.181116761572</v>
       </c>
       <c r="F13" s="156" t="n">
-        <v>7413.664273727154</v>
+        <v>3707.467910126685</v>
       </c>
       <c r="G13" s="157" t="n">
-        <v>7694.869845154931</v>
+        <v>3886.433455009673</v>
       </c>
       <c r="H13" s="155" t="n">
-        <v>6834.400158619271</v>
+        <v>3371.389819206317</v>
       </c>
       <c r="I13" s="156" t="n">
-        <v>6940.330663205697</v>
+        <v>3389.350818556633</v>
       </c>
       <c r="J13" s="156" t="n">
-        <v>7306.244288533101</v>
+        <v>3614.403781024849</v>
       </c>
       <c r="K13" s="156" t="n">
-        <v>7408.630879889043</v>
+        <v>3704.950781559107</v>
       </c>
       <c r="L13" s="157" t="n">
-        <v>7690.260878346114</v>
+        <v>3884.105612803207</v>
       </c>
       <c r="M13" s="158" t="n">
-        <v>63511781.90692843</v>
+        <v>31330178.20892842</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>72728806.67317753</v>
+        <v>35517535.45940171</v>
       </c>
       <c r="O13" s="159" t="n">
-        <v>85466913.86564566</v>
+        <v>42280537.63728397</v>
       </c>
       <c r="P13" s="159" t="n">
-        <v>99312599.84753951</v>
+        <v>49664816.66978651</v>
       </c>
       <c r="Q13" s="160" t="n">
-        <v>118406970.142038</v>
+        <v>59803585.93798702</v>
       </c>
       <c r="S13" s="32" t="inlineStr">
         <is>
@@ -2653,49 +2653,49 @@
         </is>
       </c>
       <c r="T13" s="155" t="n">
-        <v>4386.768000065688</v>
+        <v>2163.979958941911</v>
       </c>
       <c r="U13" s="156" t="n">
-        <v>4454.343666261992</v>
+        <v>2175.304619334127</v>
       </c>
       <c r="V13" s="156" t="n">
-        <v>4688.853153703286</v>
+        <v>2319.578691615037</v>
       </c>
       <c r="W13" s="156" t="n">
-        <v>4754.137855148681</v>
+        <v>2377.476627953779</v>
       </c>
       <c r="X13" s="157" t="n">
-        <v>4934.465693427146</v>
+        <v>2492.241316545185</v>
       </c>
       <c r="Y13" s="155" t="n">
-        <v>4383.722179384189</v>
+        <v>2162.47746441446</v>
       </c>
       <c r="Z13" s="156" t="n">
-        <v>4451.561386243868</v>
+        <v>2173.945876715871</v>
       </c>
       <c r="AA13" s="156" t="n">
-        <v>4686.174226246619</v>
+        <v>2318.253424467363</v>
       </c>
       <c r="AB13" s="156" t="n">
-        <v>4751.736114669531</v>
+        <v>2376.275551748257</v>
       </c>
       <c r="AC13" s="157" t="n">
-        <v>4932.266518114321</v>
+        <v>2491.130583201907</v>
       </c>
       <c r="AD13" s="158" t="n">
-        <v>63511781.90692843</v>
+        <v>31330178.20892842</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>72728806.67317753</v>
+        <v>35517535.45940171</v>
       </c>
       <c r="AF13" s="159" t="n">
-        <v>85466913.86564566</v>
+        <v>42280537.63728397</v>
       </c>
       <c r="AG13" s="159" t="n">
-        <v>99312599.84753951</v>
+        <v>49664816.66978651</v>
       </c>
       <c r="AH13" s="160" t="n">
-        <v>118406970.142038</v>
+        <v>59803585.93798702</v>
       </c>
       <c r="AJ13" s="39" t="n"/>
       <c r="AQ13" s="49" t="inlineStr">
@@ -2746,49 +2746,49 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>960.6073977513222</v>
+        <v>471.9547087738221</v>
       </c>
       <c r="D14" s="168" t="n">
-        <v>1016.825145909004</v>
+        <v>493.6393486998682</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>1094.894467951161</v>
+        <v>531.2280374329542</v>
       </c>
       <c r="F14" s="168" t="n">
-        <v>1156.998537716707</v>
+        <v>560.9126404319311</v>
       </c>
       <c r="G14" s="169" t="n">
-        <v>1228.068700983788</v>
+        <v>595.2576955186028</v>
       </c>
       <c r="H14" s="167" t="n">
-        <v>953.0363487623126</v>
+        <v>468.2349870341346</v>
       </c>
       <c r="I14" s="168" t="n">
-        <v>1010.840888361949</v>
+        <v>490.7341638606988</v>
       </c>
       <c r="J14" s="168" t="n">
-        <v>1090.510785940966</v>
+        <v>529.1011340105965</v>
       </c>
       <c r="K14" s="168" t="n">
-        <v>1154.490764232933</v>
+        <v>559.6968723902835</v>
       </c>
       <c r="L14" s="169" t="n">
-        <v>1227.607059276544</v>
+        <v>595.0339329729168</v>
       </c>
       <c r="M14" s="170" t="n">
-        <v>152718454.8624431</v>
+        <v>75031895.50456826</v>
       </c>
       <c r="N14" s="171" t="n">
-        <v>172590793.1985514</v>
+        <v>83787863.7137391</v>
       </c>
       <c r="O14" s="171" t="n">
-        <v>198326855.0164461</v>
+        <v>96225516.74572563</v>
       </c>
       <c r="P14" s="171" t="n">
-        <v>226900423.0404533</v>
+        <v>110001275.9341148</v>
       </c>
       <c r="Q14" s="172" t="n">
-        <v>265768506.5145722</v>
+        <v>128820764.3453112</v>
       </c>
       <c r="S14" s="51" t="inlineStr">
         <is>
@@ -2796,49 +2796,49 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>1083.134913962896</v>
+        <v>532.1535354388891</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>1144.671760159198</v>
+        <v>555.7052010697272</v>
       </c>
       <c r="V14" s="168" t="n">
-        <v>1230.460676113902</v>
+        <v>597.0029342951905</v>
       </c>
       <c r="W14" s="168" t="n">
-        <v>1296.618173421435</v>
+        <v>628.6002095742687</v>
       </c>
       <c r="X14" s="169" t="n">
-        <v>1373.467127139631</v>
+        <v>665.7338276895679</v>
       </c>
       <c r="Y14" s="167" t="n">
-        <v>1074.994577015421</v>
+        <v>528.1541176097533</v>
       </c>
       <c r="Z14" s="168" t="n">
-        <v>1138.249724334147</v>
+        <v>552.5874874738748</v>
       </c>
       <c r="AA14" s="168" t="n">
-        <v>1225.760061426975</v>
+        <v>594.7222594101148</v>
       </c>
       <c r="AB14" s="168" t="n">
-        <v>1293.924078959097</v>
+        <v>627.2941131625779</v>
       </c>
       <c r="AC14" s="169" t="n">
-        <v>1372.931685009227</v>
+        <v>665.474293309795</v>
       </c>
       <c r="AD14" s="170" t="n">
-        <v>152718454.8624431</v>
+        <v>75031895.50456826</v>
       </c>
       <c r="AE14" s="171" t="n">
-        <v>172590793.1985514</v>
+        <v>83787863.7137391</v>
       </c>
       <c r="AF14" s="171" t="n">
-        <v>198326855.0164461</v>
+        <v>96225516.74572563</v>
       </c>
       <c r="AG14" s="171" t="n">
-        <v>226900423.0404533</v>
+        <v>110001275.9341148</v>
       </c>
       <c r="AH14" s="172" t="n">
-        <v>265768506.5145722</v>
+        <v>128820764.3453112</v>
       </c>
       <c r="AR14" s="58" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>123534.7071570992</v>
       </c>
       <c r="E19" s="75" t="n">
-        <v>131781.8177623025</v>
+        <v>131781.8177623026</v>
       </c>
       <c r="F19" s="75" t="n">
         <v>142072.9871695138</v>
@@ -3202,7 +3202,7 @@
         </is>
       </c>
       <c r="T19" s="74" t="n">
-        <v>94022.74165982254</v>
+        <v>94022.74165982255</v>
       </c>
       <c r="U19" s="75" t="n">
         <v>100671.4901834258</v>
@@ -3232,7 +3232,7 @@
         <v>30.16412813999912</v>
       </c>
       <c r="AD19" s="74" t="n">
-        <v>94816.92580116398</v>
+        <v>94816.92580116399</v>
       </c>
       <c r="AE19" s="75" t="n">
         <v>101302.3963567819</v>
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="C20" s="79" t="n">
-        <v>25736.05101325882</v>
+        <v>25736.05101325883</v>
       </c>
       <c r="D20" s="80" t="n">
         <v>26483.14423816907</v>
@@ -3301,7 +3301,7 @@
         <v>29542.07912993147</v>
       </c>
       <c r="G20" s="81" t="n">
-        <v>32259.38220138617</v>
+        <v>32259.38220138618</v>
       </c>
       <c r="H20" s="79" t="n">
         <v>231.3841025303798</v>
@@ -3325,13 +3325,13 @@
         <v>26672.47541003757</v>
       </c>
       <c r="O20" s="80" t="n">
-        <v>27770.34595583852</v>
+        <v>27770.34595583853</v>
       </c>
       <c r="P20" s="80" t="n">
-        <v>29635.90281643001</v>
+        <v>29635.90281643002</v>
       </c>
       <c r="Q20" s="81" t="n">
-        <v>32294.10343555032</v>
+        <v>32294.10343555033</v>
       </c>
       <c r="S20" s="32" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>26179.60736526955</v>
       </c>
       <c r="V20" s="80" t="n">
-        <v>27309.07140925933</v>
+        <v>27309.07140925934</v>
       </c>
       <c r="W20" s="80" t="n">
         <v>29203.48223836126</v>
@@ -3369,13 +3369,13 @@
         <v>34.60226326579415</v>
       </c>
       <c r="AD20" s="79" t="n">
-        <v>25671.66823255158</v>
+        <v>25671.66823255159</v>
       </c>
       <c r="AE20" s="80" t="n">
-        <v>26368.28980156898</v>
+        <v>26368.28980156899</v>
       </c>
       <c r="AF20" s="80" t="n">
-        <v>27453.21801292077</v>
+        <v>27453.21801292078</v>
       </c>
       <c r="AG20" s="80" t="n">
         <v>29296.98444180949</v>
@@ -3415,7 +3415,7 @@
         <v>150017.8513952683</v>
       </c>
       <c r="E21" s="86" t="n">
-        <v>159407.5215038081</v>
+        <v>159407.5215038082</v>
       </c>
       <c r="F21" s="86" t="n">
         <v>171615.0662994452</v>
@@ -3445,7 +3445,7 @@
         <v>150990.2302680237</v>
       </c>
       <c r="O21" s="86" t="n">
-        <v>160118.3466929539</v>
+        <v>160118.346692954</v>
       </c>
       <c r="P21" s="86" t="n">
         <v>172031.9561052827</v>
@@ -3569,7 +3569,7 @@
         <v>8584.818806935771</v>
       </c>
       <c r="D22" s="80" t="n">
-        <v>9246.766475939343</v>
+        <v>9246.766475939345</v>
       </c>
       <c r="E22" s="80" t="n">
         <v>10041.54286424376</v>
@@ -3599,7 +3599,7 @@
         <v>8622.031676268572</v>
       </c>
       <c r="N22" s="80" t="n">
-        <v>9270.435732483327</v>
+        <v>9270.435732483329</v>
       </c>
       <c r="O22" s="80" t="n">
         <v>10049.88169191919</v>
@@ -3619,13 +3619,13 @@
         <v>7054.851945895035</v>
       </c>
       <c r="U22" s="80" t="n">
-        <v>7598.828808514154</v>
+        <v>7598.828808514156</v>
       </c>
       <c r="V22" s="80" t="n">
         <v>8251.961958517371</v>
       </c>
       <c r="W22" s="80" t="n">
-        <v>9122.023522871783</v>
+        <v>9122.023522871785</v>
       </c>
       <c r="X22" s="81" t="n">
         <v>10295.70244977662</v>
@@ -3649,13 +3649,13 @@
         <v>7087.706909349458</v>
       </c>
       <c r="AE22" s="80" t="n">
-        <v>7619.726217735445</v>
+        <v>7619.726217735447</v>
       </c>
       <c r="AF22" s="80" t="n">
         <v>8259.324246979435</v>
       </c>
       <c r="AG22" s="80" t="n">
-        <v>9122.023522871783</v>
+        <v>9122.023522871785</v>
       </c>
       <c r="AH22" s="81" t="n">
         <v>10295.70244977662</v>
@@ -3736,10 +3736,10 @@
         <v>150951.1467452348</v>
       </c>
       <c r="N23" s="86" t="n">
-        <v>160260.666000507</v>
+        <v>160260.6660005071</v>
       </c>
       <c r="O23" s="86" t="n">
-        <v>170168.2283848731</v>
+        <v>170168.2283848732</v>
       </c>
       <c r="P23" s="86" t="n">
         <v>183132.2484568503</v>
@@ -3762,7 +3762,7 @@
         <v>142953.2980884953</v>
       </c>
       <c r="W23" s="86" t="n">
-        <v>154104.2991247606</v>
+        <v>154104.2991247607</v>
       </c>
       <c r="X23" s="87" t="n">
         <v>169506.0006699097</v>
@@ -3786,7 +3786,7 @@
         <v>127576.300943065</v>
       </c>
       <c r="AE23" s="86" t="n">
-        <v>135290.4123760863</v>
+        <v>135290.4123760864</v>
       </c>
       <c r="AF23" s="86" t="n">
         <v>143560.9839589229</v>
@@ -3948,7 +3948,7 @@
         <v>169734.9774373071</v>
       </c>
       <c r="E25" s="92" t="n">
-        <v>181137.8729381732</v>
+        <v>181137.8729381733</v>
       </c>
       <c r="F25" s="92" t="n">
         <v>196111.2444344421</v>
@@ -3978,7 +3978,7 @@
         <v>170739.8218509265</v>
       </c>
       <c r="O25" s="92" t="n">
-        <v>181866.0187256345</v>
+        <v>181866.0187256346</v>
       </c>
       <c r="P25" s="92" t="n">
         <v>196537.2353508696</v>
@@ -3995,7 +3995,7 @@
         <v>140996.7058523558</v>
       </c>
       <c r="U25" s="92" t="n">
-        <v>150777.5409559749</v>
+        <v>150777.540955975</v>
       </c>
       <c r="V25" s="92" t="n">
         <v>161180.9778779857</v>
@@ -4031,10 +4031,10 @@
         <v>161799.0838970253</v>
       </c>
       <c r="AG25" s="92" t="n">
-        <v>175358.3743668982</v>
+        <v>175358.3743668983</v>
       </c>
       <c r="AH25" s="93" t="n">
-        <v>193577.3712679565</v>
+        <v>193577.3712679566</v>
       </c>
     </row>
     <row r="28" ht="1.95" customHeight="1">
@@ -4408,49 +4408,49 @@
         </is>
       </c>
       <c r="C35" s="148" t="n">
-        <v>471.3963863143368</v>
+        <v>460.7062978153089</v>
       </c>
       <c r="D35" s="149" t="n">
-        <v>512.3628247479872</v>
+        <v>493.4387938870528</v>
       </c>
       <c r="E35" s="149" t="n">
-        <v>550.6168724512149</v>
+        <v>523.8345687107734</v>
       </c>
       <c r="F35" s="149" t="n">
-        <v>587.3346763286985</v>
+        <v>552.3380399857756</v>
       </c>
       <c r="G35" s="150" t="n">
-        <v>621.2270646615178</v>
+        <v>578.3199913939201</v>
       </c>
       <c r="H35" s="148" t="n">
-        <v>467.4031876362208</v>
+        <v>456.8036548743656</v>
       </c>
       <c r="I35" s="149" t="n">
-        <v>509.1355742848724</v>
+        <v>490.3307413524567</v>
       </c>
       <c r="J35" s="149" t="n">
-        <v>548.2613408444639</v>
+        <v>521.5936114407683</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>586.0021398555858</v>
+        <v>551.0849033782638</v>
       </c>
       <c r="L35" s="150" t="n">
-        <v>621.0782385390934</v>
+        <v>578.1814444330168</v>
       </c>
       <c r="M35" s="151" t="n">
-        <v>54387820.12882069</v>
+        <v>53154440.6899325</v>
       </c>
       <c r="N35" s="152" t="n">
-        <v>63294591.51342676</v>
+        <v>60956816.90278932</v>
       </c>
       <c r="O35" s="152" t="n">
-        <v>72561292.34221499</v>
+        <v>69031871.6714375</v>
       </c>
       <c r="P35" s="152" t="n">
-        <v>83444391.9342577</v>
+        <v>78472315.26813348</v>
       </c>
       <c r="Q35" s="153" t="n">
-        <v>97058088.29658975</v>
+        <v>90354454.88676108</v>
       </c>
       <c r="S35" s="21" t="inlineStr">
         <is>
@@ -4458,49 +4458,49 @@
         </is>
       </c>
       <c r="T35" s="148" t="n">
-        <v>578.4538843336187</v>
+        <v>565.3360001163022</v>
       </c>
       <c r="U35" s="149" t="n">
-        <v>628.7240945584747</v>
+        <v>605.5022806528897</v>
       </c>
       <c r="V35" s="149" t="n">
-        <v>675.6659106772347</v>
+        <v>642.8011537978076</v>
       </c>
       <c r="W35" s="149" t="n">
-        <v>720.7225909865474</v>
+        <v>677.7779676951933</v>
       </c>
       <c r="X35" s="150" t="n">
-        <v>762.3121836301144</v>
+        <v>709.660606491212</v>
       </c>
       <c r="Y35" s="148" t="n">
-        <v>573.6087694181815</v>
+        <v>560.6007602629948</v>
       </c>
       <c r="Z35" s="149" t="n">
-        <v>624.8084328677321</v>
+        <v>601.7312432383386</v>
       </c>
       <c r="AA35" s="149" t="n">
-        <v>672.807981266108</v>
+        <v>640.0822356255061</v>
       </c>
       <c r="AB35" s="149" t="n">
-        <v>719.1058822122585</v>
+        <v>676.2575913380534</v>
       </c>
       <c r="AC35" s="150" t="n">
-        <v>762.1316234882189</v>
+        <v>709.4925173243887</v>
       </c>
       <c r="AD35" s="151" t="n">
-        <v>54387820.12882069</v>
+        <v>53154440.6899325</v>
       </c>
       <c r="AE35" s="152" t="n">
-        <v>63294591.51342676</v>
+        <v>60956816.90278932</v>
       </c>
       <c r="AF35" s="152" t="n">
-        <v>72561292.34221499</v>
+        <v>69031871.6714375</v>
       </c>
       <c r="AG35" s="152" t="n">
-        <v>83444391.9342577</v>
+        <v>78472315.26813348</v>
       </c>
       <c r="AH35" s="153" t="n">
-        <v>97058088.29658975</v>
+        <v>90354454.88676108</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" thickBot="1">
@@ -4510,49 +4510,49 @@
         </is>
       </c>
       <c r="C36" s="155" t="n">
-        <v>1046.503300281979</v>
+        <v>1029.194438011742</v>
       </c>
       <c r="D36" s="156" t="n">
-        <v>1126.54800055247</v>
+        <v>1095.336631810123</v>
       </c>
       <c r="E36" s="156" t="n">
-        <v>1203.99147039808</v>
+        <v>1159.491296192618</v>
       </c>
       <c r="F36" s="156" t="n">
-        <v>1272.60734872956</v>
+        <v>1214.287273673856</v>
       </c>
       <c r="G36" s="157" t="n">
-        <v>1334.38924056399</v>
+        <v>1262.03819770399</v>
       </c>
       <c r="H36" s="155" t="n">
-        <v>1037.178381365224</v>
+        <v>1020.023750560065</v>
       </c>
       <c r="I36" s="156" t="n">
-        <v>1118.551342955761</v>
+        <v>1087.561524141898</v>
       </c>
       <c r="J36" s="156" t="n">
-        <v>1197.720464894825</v>
+        <v>1153.452070435482</v>
       </c>
       <c r="K36" s="156" t="n">
-        <v>1268.578427671797</v>
+        <v>1210.442986925109</v>
       </c>
       <c r="L36" s="157" t="n">
-        <v>1332.954562515714</v>
+        <v>1260.681308392168</v>
       </c>
       <c r="M36" s="158" t="n">
-        <v>26932862.32160073</v>
+        <v>26487400.55923245</v>
       </c>
       <c r="N36" s="159" t="n">
-        <v>29834533.18985203</v>
+        <v>29007958.00957777</v>
       </c>
       <c r="O36" s="159" t="n">
-        <v>33261111.66851704</v>
+        <v>32031763.03947157</v>
       </c>
       <c r="P36" s="159" t="n">
-        <v>37595466.99750097</v>
+        <v>35872570.7253418</v>
       </c>
       <c r="Q36" s="160" t="n">
-        <v>43046572.51677119</v>
+        <v>40712572.57248159</v>
       </c>
       <c r="S36" s="32" t="inlineStr">
         <is>
@@ -4560,49 +4560,49 @@
         </is>
       </c>
       <c r="T36" s="155" t="n">
-        <v>1058.636879476449</v>
+        <v>1041.127331311514</v>
       </c>
       <c r="U36" s="156" t="n">
-        <v>1139.60965012146</v>
+        <v>1108.036404245709</v>
       </c>
       <c r="V36" s="156" t="n">
-        <v>1217.951030632247</v>
+        <v>1172.934903550436</v>
       </c>
       <c r="W36" s="156" t="n">
-        <v>1287.362468990637</v>
+        <v>1228.366207582606</v>
       </c>
       <c r="X36" s="157" t="n">
-        <v>1349.860684870251</v>
+        <v>1276.670774986987</v>
       </c>
       <c r="Y36" s="155" t="n">
-        <v>1049.127858681578</v>
+        <v>1031.775586973601</v>
       </c>
       <c r="Z36" s="156" t="n">
-        <v>1131.454994403042</v>
+        <v>1100.107675843722</v>
       </c>
       <c r="AA36" s="156" t="n">
-        <v>1211.556024246877</v>
+        <v>1166.776260050677</v>
       </c>
       <c r="AB36" s="156" t="n">
-        <v>1283.253813107426</v>
+        <v>1224.445840034934</v>
       </c>
       <c r="AC36" s="157" t="n">
-        <v>1348.397588798123</v>
+        <v>1275.287008486324</v>
       </c>
       <c r="AD36" s="158" t="n">
-        <v>26932862.32160073</v>
+        <v>26487400.55923245</v>
       </c>
       <c r="AE36" s="159" t="n">
-        <v>29834533.18985203</v>
+        <v>29007958.00957777</v>
       </c>
       <c r="AF36" s="159" t="n">
-        <v>33261111.66851704</v>
+        <v>32031763.03947157</v>
       </c>
       <c r="AG36" s="159" t="n">
-        <v>37595466.99750097</v>
+        <v>35872570.7253418</v>
       </c>
       <c r="AH36" s="160" t="n">
-        <v>43046572.51677119</v>
+        <v>40712572.57248159</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" thickTop="1">
@@ -4612,49 +4612,49 @@
         </is>
       </c>
       <c r="C37" s="161" t="n">
-        <v>576.2845432616248</v>
+        <v>564.3873209840727</v>
       </c>
       <c r="D37" s="162" t="n">
-        <v>620.7869519334829</v>
+        <v>599.6937969423861</v>
       </c>
       <c r="E37" s="162" t="n">
-        <v>663.8482488933499</v>
+        <v>633.9953959355345</v>
       </c>
       <c r="F37" s="162" t="n">
-        <v>705.2985588139469</v>
+        <v>666.2869901757858</v>
       </c>
       <c r="G37" s="163" t="n">
-        <v>743.2786492194983</v>
+        <v>695.3324933058221</v>
       </c>
       <c r="H37" s="161" t="n">
-        <v>571.3566223679329</v>
+        <v>559.5611355454159</v>
       </c>
       <c r="I37" s="162" t="n">
-        <v>616.7890766042591</v>
+        <v>595.831761781342</v>
       </c>
       <c r="J37" s="162" t="n">
-        <v>660.9011783868788</v>
+        <v>631.1808534015821</v>
       </c>
       <c r="K37" s="162" t="n">
-        <v>703.5893892741816</v>
+        <v>664.6723584512216</v>
       </c>
       <c r="L37" s="163" t="n">
-        <v>742.9942180130855</v>
+        <v>695.0664097042863</v>
       </c>
       <c r="M37" s="164" t="n">
-        <v>81320682.45042142</v>
+        <v>79641841.24916495</v>
       </c>
       <c r="N37" s="165" t="n">
-        <v>93129124.70327879</v>
+        <v>89964774.91236709</v>
       </c>
       <c r="O37" s="165" t="n">
-        <v>105822404.010732</v>
+        <v>101063634.7109091</v>
       </c>
       <c r="P37" s="165" t="n">
-        <v>121039858.9317587</v>
+        <v>114344885.9934753</v>
       </c>
       <c r="Q37" s="166" t="n">
-        <v>140104660.8133609</v>
+        <v>131067027.4592427</v>
       </c>
       <c r="S37" s="42" t="inlineStr">
         <is>
@@ -4662,49 +4662,49 @@
         </is>
       </c>
       <c r="T37" s="161" t="n">
-        <v>680.7139047714986</v>
+        <v>666.660769515344</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>734.1609690647616</v>
+        <v>709.2155815035939</v>
       </c>
       <c r="V37" s="162" t="n">
-        <v>785.6076788178283</v>
+        <v>750.2793781747592</v>
       </c>
       <c r="W37" s="162" t="n">
-        <v>834.8596987408697</v>
+        <v>788.6818269252325</v>
       </c>
       <c r="X37" s="163" t="n">
-        <v>879.9974774222479</v>
+        <v>823.2320956903304</v>
       </c>
       <c r="Y37" s="161" t="n">
-        <v>674.9243204519921</v>
+        <v>660.9907094349468</v>
       </c>
       <c r="Z37" s="162" t="n">
-        <v>729.4479845418083</v>
+        <v>704.6627351934422</v>
       </c>
       <c r="AA37" s="162" t="n">
-        <v>782.1219949262071</v>
+        <v>746.9504433727793</v>
       </c>
       <c r="AB37" s="162" t="n">
-        <v>832.8273602247499</v>
+        <v>786.76190139015</v>
       </c>
       <c r="AC37" s="163" t="n">
-        <v>879.6396419933448</v>
+        <v>822.8973429011394</v>
       </c>
       <c r="AD37" s="164" t="n">
-        <v>81320682.45042142</v>
+        <v>79641841.24916495</v>
       </c>
       <c r="AE37" s="165" t="n">
-        <v>93129124.70327879</v>
+        <v>89964774.91236709</v>
       </c>
       <c r="AF37" s="165" t="n">
-        <v>105822404.010732</v>
+        <v>101063634.7109091</v>
       </c>
       <c r="AG37" s="165" t="n">
-        <v>121039858.9317587</v>
+        <v>114344885.9934753</v>
       </c>
       <c r="AH37" s="166" t="n">
-        <v>140104660.8133609</v>
+        <v>131067027.4592427</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" thickBot="1">
@@ -4714,49 +4714,49 @@
         </is>
       </c>
       <c r="C38" s="155" t="n">
-        <v>1212.942720733083</v>
+        <v>1192.445851264407</v>
       </c>
       <c r="D38" s="156" t="n">
-        <v>1295.223969473461</v>
+        <v>1259.284161266991</v>
       </c>
       <c r="E38" s="156" t="n">
-        <v>1366.544511769841</v>
+        <v>1316.047905054163</v>
       </c>
       <c r="F38" s="156" t="n">
-        <v>1425.147809083238</v>
+        <v>1359.885058509356</v>
       </c>
       <c r="G38" s="157" t="n">
-        <v>1465.747624492744</v>
+        <v>1386.300910065538</v>
       </c>
       <c r="H38" s="155" t="n">
-        <v>1207.707634541153</v>
+        <v>1187.299229990482</v>
       </c>
       <c r="I38" s="156" t="n">
-        <v>1291.917006424469</v>
+        <v>1256.068959658898</v>
       </c>
       <c r="J38" s="156" t="n">
-        <v>1365.410629845278</v>
+        <v>1314.955922379215</v>
       </c>
       <c r="K38" s="156" t="n">
-        <v>1425.147809083238</v>
+        <v>1359.885058509356</v>
       </c>
       <c r="L38" s="157" t="n">
-        <v>1465.747624492744</v>
+        <v>1386.300910065538</v>
       </c>
       <c r="M38" s="158" t="n">
-        <v>10412893.48068521</v>
+        <v>10236931.57018722</v>
       </c>
       <c r="N38" s="159" t="n">
-        <v>11976633.57976029</v>
+        <v>11644306.56608501</v>
       </c>
       <c r="O38" s="159" t="n">
-        <v>13722215.29083391</v>
+        <v>13215151.44999958</v>
       </c>
       <c r="P38" s="159" t="n">
-        <v>15819557.32501994</v>
+        <v>15095121.71398241</v>
       </c>
       <c r="Q38" s="160" t="n">
-        <v>18363624.80980064</v>
+        <v>17368276.33934518</v>
       </c>
       <c r="S38" s="32" t="inlineStr">
         <is>
@@ -4764,49 +4764,49 @@
         </is>
       </c>
       <c r="T38" s="155" t="n">
-        <v>1475.990362454608</v>
+        <v>1451.04839175877</v>
       </c>
       <c r="U38" s="156" t="n">
-        <v>1576.115725405077</v>
+        <v>1532.381747176364</v>
       </c>
       <c r="V38" s="156" t="n">
-        <v>1662.9033628385</v>
+        <v>1601.455692165351</v>
       </c>
       <c r="W38" s="156" t="n">
-        <v>1734.215800403861</v>
+        <v>1654.799691771698</v>
       </c>
       <c r="X38" s="157" t="n">
-        <v>1783.620389126442</v>
+        <v>1686.944278359754</v>
       </c>
       <c r="Y38" s="155" t="n">
-        <v>1469.148430354741</v>
+        <v>1444.322077805389</v>
       </c>
       <c r="Z38" s="156" t="n">
-        <v>1571.793163891353</v>
+        <v>1528.179127877596</v>
       </c>
       <c r="AA38" s="156" t="n">
-        <v>1661.421065512998</v>
+        <v>1600.028168749104</v>
       </c>
       <c r="AB38" s="156" t="n">
-        <v>1734.215800403861</v>
+        <v>1654.799691771698</v>
       </c>
       <c r="AC38" s="157" t="n">
-        <v>1783.620389126442</v>
+        <v>1686.944278359754</v>
       </c>
       <c r="AD38" s="158" t="n">
-        <v>10412893.48068521</v>
+        <v>10236931.57018722</v>
       </c>
       <c r="AE38" s="159" t="n">
-        <v>11976633.57976029</v>
+        <v>11644306.56608501</v>
       </c>
       <c r="AF38" s="159" t="n">
-        <v>13722215.29083391</v>
+        <v>13215151.44999958</v>
       </c>
       <c r="AG38" s="159" t="n">
-        <v>15819557.32501994</v>
+        <v>15095121.71398241</v>
       </c>
       <c r="AH38" s="160" t="n">
-        <v>18363624.80980064</v>
+        <v>17368276.33934518</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" thickTop="1">
@@ -4816,49 +4816,49 @@
         </is>
       </c>
       <c r="C39" s="161" t="n">
-        <v>612.7956328082067</v>
+        <v>600.4052377422186</v>
       </c>
       <c r="D39" s="162" t="n">
-        <v>659.9441840122635</v>
+        <v>637.9890451287819</v>
       </c>
       <c r="E39" s="162" t="n">
-        <v>705.4899933935842</v>
+        <v>674.4137926467945</v>
       </c>
       <c r="F39" s="162" t="n">
-        <v>749.0307178729333</v>
+        <v>708.4243419005005</v>
       </c>
       <c r="G39" s="163" t="n">
-        <v>788.3053942328077</v>
+        <v>738.3960154479638</v>
       </c>
       <c r="H39" s="161" t="n">
-        <v>607.7037366660644</v>
+        <v>595.4162969761568</v>
       </c>
       <c r="I39" s="162" t="n">
-        <v>655.8425152351891</v>
+        <v>634.0238313881124</v>
       </c>
       <c r="J39" s="162" t="n">
-        <v>702.5084555219632</v>
+        <v>671.5635888412839</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>747.3255934441579</v>
+        <v>706.811655501278</v>
       </c>
       <c r="L39" s="163" t="n">
-        <v>788.0225264373818</v>
+        <v>738.1310566457419</v>
       </c>
       <c r="M39" s="164" t="n">
-        <v>91733575.93110664</v>
+        <v>89878772.81935216</v>
       </c>
       <c r="N39" s="165" t="n">
-        <v>105105758.2830391</v>
+        <v>101609081.4784521</v>
       </c>
       <c r="O39" s="165" t="n">
-        <v>119544619.3015659</v>
+        <v>114278786.1609087</v>
       </c>
       <c r="P39" s="165" t="n">
-        <v>136859416.2567786</v>
+        <v>129440007.7074577</v>
       </c>
       <c r="Q39" s="166" t="n">
-        <v>158468285.6231616</v>
+        <v>148435303.7985879</v>
       </c>
       <c r="S39" s="42" t="inlineStr">
         <is>
@@ -4866,49 +4866,49 @@
         </is>
       </c>
       <c r="T39" s="161" t="n">
-        <v>725.0595941468353</v>
+        <v>710.3992827201773</v>
       </c>
       <c r="U39" s="162" t="n">
-        <v>781.7464920270153</v>
+        <v>755.7392125935038</v>
       </c>
       <c r="V39" s="162" t="n">
-        <v>836.2494667843325</v>
+        <v>799.413428644118</v>
       </c>
       <c r="W39" s="162" t="n">
-        <v>888.0960299879705</v>
+        <v>839.9506596676117</v>
       </c>
       <c r="X39" s="163" t="n">
-        <v>934.8830424697319</v>
+        <v>875.6935047252148</v>
       </c>
       <c r="Y39" s="161" t="n">
-        <v>719.0487202795264</v>
+        <v>704.5099454597246</v>
       </c>
       <c r="Z39" s="162" t="n">
-        <v>776.8899246966695</v>
+        <v>751.0442143970602</v>
       </c>
       <c r="AA39" s="162" t="n">
-        <v>832.709668079255</v>
+        <v>796.0295548936003</v>
       </c>
       <c r="AB39" s="162" t="n">
-        <v>886.0617757815315</v>
+        <v>838.026686240264</v>
       </c>
       <c r="AC39" s="163" t="n">
-        <v>934.5259703039537</v>
+        <v>875.3590395974015</v>
       </c>
       <c r="AD39" s="164" t="n">
-        <v>91733575.93110664</v>
+        <v>89878772.81935216</v>
       </c>
       <c r="AE39" s="165" t="n">
-        <v>105105758.2830391</v>
+        <v>101609081.4784521</v>
       </c>
       <c r="AF39" s="165" t="n">
-        <v>119544619.3015659</v>
+        <v>114278786.1609087</v>
       </c>
       <c r="AG39" s="165" t="n">
-        <v>136859416.2567786</v>
+        <v>129440007.7074577</v>
       </c>
       <c r="AH39" s="166" t="n">
-        <v>158468285.6231616</v>
+        <v>148435303.7985879</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" thickBot="1">
@@ -4918,49 +4918,49 @@
         </is>
       </c>
       <c r="C40" s="155" t="n">
-        <v>7036.394727151741</v>
+        <v>6942.06631056527</v>
       </c>
       <c r="D40" s="156" t="n">
-        <v>7312.518501574925</v>
+        <v>7142.221825372106</v>
       </c>
       <c r="E40" s="156" t="n">
-        <v>7747.254145988883</v>
+        <v>7665.143286208036</v>
       </c>
       <c r="F40" s="156" t="n">
-        <v>7954.575400994801</v>
+        <v>7955.939721301899</v>
       </c>
       <c r="G40" s="157" t="n">
-        <v>8276.723507749737</v>
+        <v>8360.61838229466</v>
       </c>
       <c r="H40" s="155" t="n">
-        <v>7029.829416395053</v>
+        <v>6935.589012973292</v>
       </c>
       <c r="I40" s="156" t="n">
-        <v>7306.380317092007</v>
+        <v>7136.226589233885</v>
       </c>
       <c r="J40" s="156" t="n">
-        <v>7741.305667019603</v>
+        <v>7659.25785341142</v>
       </c>
       <c r="K40" s="156" t="n">
-        <v>7949.174763829446</v>
+        <v>7950.538157852162</v>
       </c>
       <c r="L40" s="157" t="n">
-        <v>8271.766030274404</v>
+        <v>8355.610654626669</v>
       </c>
       <c r="M40" s="158" t="n">
-        <v>65327897.4562111</v>
+        <v>64452125.50695007</v>
       </c>
       <c r="N40" s="159" t="n">
-        <v>76564698.04524426</v>
+        <v>74781630.61248913</v>
       </c>
       <c r="O40" s="159" t="n">
-        <v>90556170.6565434</v>
+        <v>89596392.53503701</v>
       </c>
       <c r="P40" s="159" t="n">
-        <v>106558583.5274029</v>
+        <v>106576859.8064088</v>
       </c>
       <c r="Q40" s="160" t="n">
-        <v>127360406.7355469</v>
+        <v>128651362.6718017</v>
       </c>
       <c r="S40" s="32" t="inlineStr">
         <is>
@@ -4968,49 +4968,49 @@
         </is>
       </c>
       <c r="T40" s="155" t="n">
-        <v>4512.207364807332</v>
+        <v>4451.717669084367</v>
       </c>
       <c r="U40" s="156" t="n">
-        <v>4689.276414635216</v>
+        <v>4580.070784996582</v>
       </c>
       <c r="V40" s="156" t="n">
-        <v>4968.058014095451</v>
+        <v>4915.403033725443</v>
       </c>
       <c r="W40" s="156" t="n">
-        <v>5101.00628234837</v>
+        <v>5101.88117586648</v>
       </c>
       <c r="X40" s="157" t="n">
-        <v>5307.589215259919</v>
+        <v>5361.388225331149</v>
       </c>
       <c r="Y40" s="155" t="n">
-        <v>4509.074449068287</v>
+        <v>4448.626752549804</v>
       </c>
       <c r="Z40" s="156" t="n">
-        <v>4686.347390508336</v>
+        <v>4577.209973083211</v>
       </c>
       <c r="AA40" s="156" t="n">
-        <v>4965.219565847234</v>
+        <v>4912.594669352327</v>
       </c>
       <c r="AB40" s="156" t="n">
-        <v>5098.429307585334</v>
+        <v>5099.303759116433</v>
       </c>
       <c r="AC40" s="157" t="n">
-        <v>5305.223747568379</v>
+        <v>5358.998780686044</v>
       </c>
       <c r="AD40" s="158" t="n">
-        <v>65327897.4562111</v>
+        <v>64452125.50695007</v>
       </c>
       <c r="AE40" s="159" t="n">
-        <v>76564698.04524426</v>
+        <v>74781630.61248913</v>
       </c>
       <c r="AF40" s="159" t="n">
-        <v>90556170.6565434</v>
+        <v>89596392.53503701</v>
       </c>
       <c r="AG40" s="159" t="n">
-        <v>106558583.5274029</v>
+        <v>106576859.8064088</v>
       </c>
       <c r="AH40" s="160" t="n">
-        <v>127360406.7355469</v>
+        <v>128651362.6718017</v>
       </c>
     </row>
     <row r="41" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -5020,49 +5020,49 @@
         </is>
       </c>
       <c r="C41" s="179" t="n">
-        <v>987.9252207827519</v>
+        <v>970.7497549486495</v>
       </c>
       <c r="D41" s="180" t="n">
-        <v>1070.318322547188</v>
+        <v>1039.212510904492</v>
       </c>
       <c r="E41" s="180" t="n">
-        <v>1159.894320001328</v>
+        <v>1125.524857882885</v>
       </c>
       <c r="F41" s="180" t="n">
-        <v>1241.224084249557</v>
+        <v>1203.484625241692</v>
       </c>
       <c r="G41" s="181" t="n">
-        <v>1320.763229369344</v>
+        <v>1280.367892399477</v>
       </c>
       <c r="H41" s="179" t="n">
-        <v>980.1388657520356</v>
+        <v>963.0987687413918</v>
       </c>
       <c r="I41" s="180" t="n">
-        <v>1064.019244947441</v>
+        <v>1033.096498395954</v>
       </c>
       <c r="J41" s="180" t="n">
-        <v>1155.250394935352</v>
+        <v>1121.018539497004</v>
       </c>
       <c r="K41" s="180" t="n">
-        <v>1238.533753411244</v>
+        <v>1200.876094000791</v>
       </c>
       <c r="L41" s="181" t="n">
-        <v>1320.266742982562</v>
+        <v>1279.886590971247</v>
       </c>
       <c r="M41" s="182" t="n">
-        <v>157061473.3873177</v>
+        <v>154330898.3263022</v>
       </c>
       <c r="N41" s="183" t="n">
-        <v>181670456.3282833</v>
+        <v>176390712.0909413</v>
       </c>
       <c r="O41" s="183" t="n">
-        <v>210100789.9581093</v>
+        <v>203875178.6959457</v>
       </c>
       <c r="P41" s="183" t="n">
-        <v>243417999.7841815</v>
+        <v>236016867.5138665</v>
       </c>
       <c r="Q41" s="184" t="n">
-        <v>285828692.3587085</v>
+        <v>277086666.4703895</v>
       </c>
       <c r="S41" s="51" t="inlineStr">
         <is>
@@ -5070,49 +5070,49 @@
         </is>
       </c>
       <c r="T41" s="185" t="n">
-        <v>1113.937183410399</v>
+        <v>1094.570950387375</v>
       </c>
       <c r="U41" s="186" t="n">
-        <v>1204.890696428911</v>
+        <v>1169.8739147261</v>
       </c>
       <c r="V41" s="186" t="n">
-        <v>1303.508594650394</v>
+        <v>1264.883619519169</v>
       </c>
       <c r="W41" s="186" t="n">
-        <v>1391.007553131772</v>
+        <v>1348.713922837942</v>
       </c>
       <c r="X41" s="187" t="n">
-        <v>1477.136317227518</v>
+        <v>1431.95833380249</v>
       </c>
       <c r="Y41" s="185" t="n">
-        <v>1105.565350968856</v>
+        <v>1086.344665522758</v>
       </c>
       <c r="Z41" s="186" t="n">
-        <v>1198.130809894574</v>
+        <v>1163.310485407185</v>
       </c>
       <c r="AA41" s="186" t="n">
-        <v>1298.528921781936</v>
+        <v>1260.051502057324</v>
       </c>
       <c r="AB41" s="186" t="n">
-        <v>1388.117337783274</v>
+        <v>1345.911584581948</v>
       </c>
       <c r="AC41" s="187" t="n">
-        <v>1476.560459967475</v>
+        <v>1431.400089046754</v>
       </c>
       <c r="AD41" s="188" t="n">
-        <v>157061473.3873177</v>
+        <v>154330898.3263022</v>
       </c>
       <c r="AE41" s="189" t="n">
-        <v>181670456.3282833</v>
+        <v>176390712.0909413</v>
       </c>
       <c r="AF41" s="189" t="n">
-        <v>210100789.9581093</v>
+        <v>203875178.6959457</v>
       </c>
       <c r="AG41" s="189" t="n">
-        <v>243417999.7841815</v>
+        <v>236016867.5138665</v>
       </c>
       <c r="AH41" s="190" t="n">
-        <v>285828692.3587085</v>
+        <v>277086666.4703895</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" thickBot="1"/>
@@ -5383,7 +5383,7 @@
         <v>0.2141963817335411</v>
       </c>
       <c r="G46" s="150" t="n">
-        <v>0.2323322653354023</v>
+        <v>0.2323322653354022</v>
       </c>
       <c r="H46" s="148" t="n">
         <v>0.1572947229889338</v>
@@ -5392,13 +5392,13 @@
         <v>0.173828389278059</v>
       </c>
       <c r="J46" s="149" t="n">
-        <v>0.1935342143360962</v>
+        <v>0.1935342143360961</v>
       </c>
       <c r="K46" s="149" t="n">
         <v>0.2137104160608639</v>
       </c>
       <c r="L46" s="150" t="n">
-        <v>0.2322766059603833</v>
+        <v>0.2322766059603832</v>
       </c>
       <c r="M46" s="151" t="n">
         <v>18303.07821476196</v>
@@ -5433,13 +5433,13 @@
         <v>0.2628419152567548</v>
       </c>
       <c r="X46" s="150" t="n">
-        <v>0.2850965880117631</v>
+        <v>0.285096588011763</v>
       </c>
       <c r="Y46" s="148" t="n">
         <v>0.1930359802335763</v>
       </c>
       <c r="Z46" s="149" t="n">
-        <v>0.2133212625051748</v>
+        <v>0.2133212625051747</v>
       </c>
       <c r="AA46" s="149" t="n">
         <v>0.2374987152164185</v>
@@ -5448,7 +5448,7 @@
         <v>0.262252314159244</v>
       </c>
       <c r="AC46" s="150" t="n">
-        <v>0.2850290604535124</v>
+        <v>0.2850290604535123</v>
       </c>
       <c r="AD46" s="151" t="n">
         <v>18303.07821476196</v>
@@ -5476,7 +5476,7 @@
         <v>0.02627880848523096</v>
       </c>
       <c r="D47" s="156" t="n">
-        <v>0.02644945016580756</v>
+        <v>0.02644945016580755</v>
       </c>
       <c r="E47" s="156" t="n">
         <v>0.0263322553408971</v>
@@ -5485,7 +5485,7 @@
         <v>0.02561395905656326</v>
       </c>
       <c r="G47" s="157" t="n">
-        <v>0.02439925905099968</v>
+        <v>0.02439925905099967</v>
       </c>
       <c r="H47" s="155" t="n">
         <v>0.02604464987504055</v>
@@ -5538,13 +5538,13 @@
         <v>0.02468215385114212</v>
       </c>
       <c r="Y47" s="155" t="n">
-        <v>0.02634471393199141</v>
+        <v>0.0263447139319914</v>
       </c>
       <c r="Z47" s="156" t="n">
-        <v>0.02656465811899818</v>
+        <v>0.02656465811899817</v>
       </c>
       <c r="AA47" s="156" t="n">
-        <v>0.0264976981769835</v>
+        <v>0.02649769817698349</v>
       </c>
       <c r="AB47" s="156" t="n">
         <v>0.02582824204254794</v>
@@ -5581,13 +5581,13 @@
         <v>0.1487184323857965</v>
       </c>
       <c r="E48" s="162" t="n">
-        <v>0.1652451100048923</v>
+        <v>0.1652451100048922</v>
       </c>
       <c r="F48" s="162" t="n">
         <v>0.1817335160110374</v>
       </c>
       <c r="G48" s="163" t="n">
-        <v>0.1967463162252991</v>
+        <v>0.196746316225299</v>
       </c>
       <c r="H48" s="161" t="n">
         <v>0.1333486192288132</v>
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="T48" s="161" t="n">
-        <v>0.1588714574006971</v>
+        <v>0.158871457400697</v>
       </c>
       <c r="U48" s="162" t="n">
         <v>0.175878806888724</v>
@@ -5637,7 +5637,7 @@
         <v>0.2151173946579932</v>
       </c>
       <c r="X48" s="163" t="n">
-        <v>0.232935874254144</v>
+        <v>0.2329358742541439</v>
       </c>
       <c r="Y48" s="161" t="n">
         <v>0.1575202293853196</v>
@@ -5649,7 +5649,7 @@
         <v>0.1946858115605125</v>
       </c>
       <c r="AB48" s="162" t="n">
-        <v>0.2145937241929916</v>
+        <v>0.2145937241929915</v>
       </c>
       <c r="AC48" s="163" t="n">
         <v>0.2328411549957265</v>
@@ -5719,7 +5719,7 @@
         <v>1751.331916764923</v>
       </c>
       <c r="Q49" s="160" t="n">
-        <v>1944.252913651833</v>
+        <v>1944.252913651834</v>
       </c>
       <c r="S49" s="32" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>0.1888412105085668</v>
       </c>
       <c r="Y49" s="155" t="n">
-        <v>0.187014867719193</v>
+        <v>0.1870148677191931</v>
       </c>
       <c r="Z49" s="156" t="n">
         <v>0.1896093637350641</v>
@@ -5769,7 +5769,7 @@
         <v>1751.331916764923</v>
       </c>
       <c r="AH49" s="160" t="n">
-        <v>1944.252913651833</v>
+        <v>1944.252913651834</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" thickTop="1">
@@ -5791,7 +5791,7 @@
         <v>0.1802779008783004</v>
       </c>
       <c r="G50" s="163" t="n">
-        <v>0.1941561571758201</v>
+        <v>0.19415615717582</v>
       </c>
       <c r="H50" s="161" t="n">
         <v>0.134513039340199</v>
@@ -5838,10 +5838,10 @@
         <v>0.1953625521188488</v>
       </c>
       <c r="W50" s="162" t="n">
-        <v>0.2137483607070755</v>
+        <v>0.2137483607070754</v>
       </c>
       <c r="X50" s="163" t="n">
-        <v>0.230257588318819</v>
+        <v>0.2302575883188189</v>
       </c>
       <c r="Y50" s="161" t="n">
         <v>0.1591588515303609</v>
@@ -5853,7 +5853,7 @@
         <v>0.1945355930157594</v>
       </c>
       <c r="AB50" s="162" t="n">
-        <v>0.2132587531790544</v>
+        <v>0.2132587531790543</v>
       </c>
       <c r="AC50" s="163" t="n">
         <v>0.2301696430122802</v>
@@ -5989,7 +5989,7 @@
         <v>0.1399546015089556</v>
       </c>
       <c r="E52" s="180" t="n">
-        <v>0.1541793590449602</v>
+        <v>0.1541793590449601</v>
       </c>
       <c r="F52" s="180" t="n">
         <v>0.1679635525786576</v>
@@ -6334,46 +6334,46 @@
         </is>
       </c>
       <c r="C57" s="148" t="n">
-        <v>0.009019043059663841</v>
+        <v>0.009271777981888996</v>
       </c>
       <c r="D57" s="149" t="n">
-        <v>0.008261989517174091</v>
+        <v>0.008672994390235948</v>
       </c>
       <c r="E57" s="149" t="n">
-        <v>0.007606224730456797</v>
+        <v>0.008154203174971069</v>
       </c>
       <c r="F57" s="149" t="n">
-        <v>0.0002754868115453999</v>
+        <v>0.0003025072061057304</v>
       </c>
       <c r="G57" s="150" t="n">
         <v>0</v>
       </c>
       <c r="H57" s="148" t="n">
-        <v>0.008942642748016764</v>
+        <v>0.009193236752774914</v>
       </c>
       <c r="I57" s="149" t="n">
-        <v>0.008209949228129575</v>
+        <v>0.008618365280139506</v>
       </c>
       <c r="J57" s="149" t="n">
-        <v>0.007573685402918792</v>
+        <v>0.008119319602985694</v>
       </c>
       <c r="K57" s="149" t="n">
-        <v>0.0002748617910263656</v>
+        <v>0.0003018208821038258</v>
       </c>
       <c r="L57" s="150" t="n">
         <v>0</v>
       </c>
       <c r="M57" s="151" t="n">
-        <v>1040.580933380327</v>
+        <v>1069.74047276018</v>
       </c>
       <c r="N57" s="152" t="n">
-        <v>1020.642455539125</v>
+        <v>1071.415822172962</v>
       </c>
       <c r="O57" s="152" t="n">
-        <v>1002.362121288176</v>
+        <v>1074.575716800826</v>
       </c>
       <c r="P57" s="152" t="n">
-        <v>39.13923424205985</v>
+        <v>42.9781024117449</v>
       </c>
       <c r="Q57" s="153" t="n">
         <v>0</v>
@@ -6384,46 +6384,46 @@
         </is>
       </c>
       <c r="T57" s="148" t="n">
-        <v>0.01106733238161873</v>
+        <v>0.01137746521613395</v>
       </c>
       <c r="U57" s="149" t="n">
-        <v>0.01013834655352266</v>
+        <v>0.01064269357909392</v>
       </c>
       <c r="V57" s="149" t="n">
-        <v>0.009333652883612169</v>
+        <v>0.01000608116045731</v>
       </c>
       <c r="W57" s="149" t="n">
-        <v>0.0003380518409720221</v>
+        <v>0.0003712087608030278</v>
       </c>
       <c r="X57" s="150" t="n">
         <v>0</v>
       </c>
       <c r="Y57" s="148" t="n">
-        <v>0.01097463268913062</v>
+        <v>0.01128216785896941</v>
       </c>
       <c r="Z57" s="149" t="n">
-        <v>0.01007520544671494</v>
+        <v>0.01057641142465663</v>
       </c>
       <c r="AA57" s="149" t="n">
-        <v>0.009294173429835099</v>
+        <v>0.009963757471801876</v>
       </c>
       <c r="AB57" s="149" t="n">
-        <v>0.0003372935306536015</v>
+        <v>0.000370376073624648</v>
       </c>
       <c r="AC57" s="150" t="n">
         <v>0</v>
       </c>
       <c r="AD57" s="151" t="n">
-        <v>1040.580933380327</v>
+        <v>1069.74047276018</v>
       </c>
       <c r="AE57" s="152" t="n">
-        <v>1020.642455539125</v>
+        <v>1071.415822172962</v>
       </c>
       <c r="AF57" s="152" t="n">
-        <v>1002.362121288176</v>
+        <v>1074.575716800826</v>
       </c>
       <c r="AG57" s="152" t="n">
-        <v>39.13923424205985</v>
+        <v>42.9781024117449</v>
       </c>
       <c r="AH57" s="153" t="n">
         <v>0</v>
@@ -6538,46 +6538,46 @@
         </is>
       </c>
       <c r="C59" s="161" t="n">
-        <v>0.007374147508973949</v>
+        <v>0.007580788566659154</v>
       </c>
       <c r="D59" s="162" t="n">
-        <v>0.006803473360313152</v>
+        <v>0.007141922192646172</v>
       </c>
       <c r="E59" s="162" t="n">
-        <v>0.006288047840102896</v>
+        <v>0.006741060312986268</v>
       </c>
       <c r="F59" s="162" t="n">
-        <v>0.000228064091842421</v>
+        <v>0.000250433154492123</v>
       </c>
       <c r="G59" s="163" t="n">
         <v>0</v>
       </c>
       <c r="H59" s="161" t="n">
-        <v>0.007311089743487185</v>
+        <v>0.007515963773412287</v>
       </c>
       <c r="I59" s="162" t="n">
-        <v>0.006759658911224761</v>
+        <v>0.007095928129065602</v>
       </c>
       <c r="J59" s="162" t="n">
-        <v>0.006260132845427925</v>
+        <v>0.006711134226619599</v>
       </c>
       <c r="K59" s="162" t="n">
-        <v>0.0002275114178095309</v>
+        <v>0.0002498262728899189</v>
       </c>
       <c r="L59" s="163" t="n">
         <v>0</v>
       </c>
       <c r="M59" s="164" t="n">
-        <v>1040.580933380327</v>
+        <v>1069.74047276018</v>
       </c>
       <c r="N59" s="165" t="n">
-        <v>1020.642455539125</v>
+        <v>1071.415822172962</v>
       </c>
       <c r="O59" s="165" t="n">
-        <v>1002.362121288176</v>
+        <v>1074.575716800826</v>
       </c>
       <c r="P59" s="165" t="n">
-        <v>39.13923424205985</v>
+        <v>42.9781024117449</v>
       </c>
       <c r="Q59" s="166" t="n">
         <v>0</v>
@@ -6588,46 +6588,46 @@
         </is>
       </c>
       <c r="T59" s="161" t="n">
-        <v>0.008710427520378266</v>
+        <v>0.008954514305123333</v>
       </c>
       <c r="U59" s="162" t="n">
-        <v>0.00804598836953163</v>
+        <v>0.008446247946429231</v>
       </c>
       <c r="V59" s="162" t="n">
-        <v>0.007441367324827149</v>
+        <v>0.007977468877991912</v>
       </c>
       <c r="W59" s="162" t="n">
-        <v>0.0002699587524031795</v>
+        <v>0.0002964369419180572</v>
       </c>
       <c r="X59" s="163" t="n">
         <v>0</v>
       </c>
       <c r="Y59" s="161" t="n">
-        <v>0.008636343894005</v>
+        <v>0.008878354680284846</v>
       </c>
       <c r="Z59" s="162" t="n">
-        <v>0.007994336728739867</v>
+        <v>0.008392026818466982</v>
       </c>
       <c r="AA59" s="162" t="n">
-        <v>0.007408350521510234</v>
+        <v>0.007942073431239444</v>
       </c>
       <c r="AB59" s="162" t="n">
-        <v>0.0002693015790229096</v>
+        <v>0.0002957153114266472</v>
       </c>
       <c r="AC59" s="163" t="n">
         <v>0</v>
       </c>
       <c r="AD59" s="164" t="n">
-        <v>1040.580933380327</v>
+        <v>1069.74047276018</v>
       </c>
       <c r="AE59" s="165" t="n">
-        <v>1020.642455539125</v>
+        <v>1071.415822172962</v>
       </c>
       <c r="AF59" s="165" t="n">
-        <v>1002.362121288176</v>
+        <v>1074.575716800826</v>
       </c>
       <c r="AG59" s="165" t="n">
-        <v>39.13923424205985</v>
+        <v>42.9781024117449</v>
       </c>
       <c r="AH59" s="166" t="n">
         <v>0</v>
@@ -6742,46 +6742,46 @@
         </is>
       </c>
       <c r="C61" s="161" t="n">
-        <v>0.006951254707849248</v>
+        <v>0.007146045308840237</v>
       </c>
       <c r="D61" s="162" t="n">
-        <v>0.006408469559538245</v>
+        <v>0.006727268344305971</v>
       </c>
       <c r="E61" s="162" t="n">
-        <v>0.005915418447581366</v>
+        <v>0.006341585424554448</v>
       </c>
       <c r="F61" s="162" t="n">
-        <v>0.0002142087809750902</v>
+        <v>0.0002352188821402435</v>
       </c>
       <c r="G61" s="163" t="n">
         <v>0</v>
       </c>
       <c r="H61" s="161" t="n">
-        <v>0.006893494722080839</v>
+        <v>0.007086666751632005</v>
       </c>
       <c r="I61" s="162" t="n">
-        <v>0.006368639797964499</v>
+        <v>0.006685457192406602</v>
       </c>
       <c r="J61" s="162" t="n">
-        <v>0.005890418739161534</v>
+        <v>0.006314784651635646</v>
       </c>
       <c r="K61" s="162" t="n">
-        <v>0.0002137211472685099</v>
+        <v>0.0002346834201725614</v>
       </c>
       <c r="L61" s="163" t="n">
         <v>0</v>
       </c>
       <c r="M61" s="164" t="n">
-        <v>1040.580933380327</v>
+        <v>1069.74047276018</v>
       </c>
       <c r="N61" s="165" t="n">
-        <v>1020.642455539125</v>
+        <v>1071.415822172962</v>
       </c>
       <c r="O61" s="165" t="n">
-        <v>1002.362121288176</v>
+        <v>1074.575716800826</v>
       </c>
       <c r="P61" s="165" t="n">
-        <v>39.13923424205985</v>
+        <v>42.9781024117449</v>
       </c>
       <c r="Q61" s="166" t="n">
         <v>0</v>
@@ -6792,46 +6792,46 @@
         </is>
       </c>
       <c r="T61" s="161" t="n">
-        <v>0.008224722317598339</v>
+        <v>0.008455198493564084</v>
       </c>
       <c r="U61" s="162" t="n">
-        <v>0.00759124592472784</v>
+        <v>0.007968883666967588</v>
       </c>
       <c r="V61" s="162" t="n">
-        <v>0.007011815289967383</v>
+        <v>0.007516970445380069</v>
       </c>
       <c r="W61" s="162" t="n">
-        <v>0.0002539788601898334</v>
+        <v>0.0002788897042836581</v>
       </c>
       <c r="X61" s="163" t="n">
         <v>0</v>
       </c>
       <c r="Y61" s="161" t="n">
-        <v>0.008156537896836489</v>
+        <v>0.008385103384033567</v>
       </c>
       <c r="Z61" s="162" t="n">
-        <v>0.007544085627456714</v>
+        <v>0.007919377311043981</v>
       </c>
       <c r="AA61" s="162" t="n">
-        <v>0.006982134655575935</v>
+        <v>0.007485151516572879</v>
       </c>
       <c r="AB61" s="162" t="n">
-        <v>0.0002533971015204531</v>
+        <v>0.0002782508853553951</v>
       </c>
       <c r="AC61" s="163" t="n">
         <v>0</v>
       </c>
       <c r="AD61" s="164" t="n">
-        <v>1040.580933380327</v>
+        <v>1069.74047276018</v>
       </c>
       <c r="AE61" s="165" t="n">
-        <v>1020.642455539125</v>
+        <v>1071.415822172962</v>
       </c>
       <c r="AF61" s="165" t="n">
-        <v>1002.362121288176</v>
+        <v>1074.575716800826</v>
       </c>
       <c r="AG61" s="165" t="n">
-        <v>39.13923424205985</v>
+        <v>42.9781024117449</v>
       </c>
       <c r="AH61" s="166" t="n">
         <v>0</v>
@@ -6946,46 +6946,46 @@
         </is>
       </c>
       <c r="C63" s="179" t="n">
-        <v>0.006545310738407287</v>
+        <v>0.006728725829062424</v>
       </c>
       <c r="D63" s="180" t="n">
-        <v>0.006013153393301667</v>
+        <v>0.006312286591422783</v>
       </c>
       <c r="E63" s="180" t="n">
-        <v>0.005533697095086829</v>
+        <v>0.005932363560256693</v>
       </c>
       <c r="F63" s="180" t="n">
-        <v>0.000199576696149841</v>
+        <v>0.0002191516480132888</v>
       </c>
       <c r="G63" s="181" t="n">
         <v>0</v>
       </c>
       <c r="H63" s="179" t="n">
-        <v>0.006493723723394937</v>
+        <v>0.006675693223853785</v>
       </c>
       <c r="I63" s="180" t="n">
-        <v>0.005977764557059521</v>
+        <v>0.006275137285245727</v>
       </c>
       <c r="J63" s="180" t="n">
-        <v>0.005511541564014513</v>
+        <v>0.005908611868949224</v>
       </c>
       <c r="K63" s="180" t="n">
-        <v>0.0001991441172568966</v>
+        <v>0.0002186766407648806</v>
       </c>
       <c r="L63" s="181" t="n">
         <v>0</v>
       </c>
       <c r="M63" s="182" t="n">
-        <v>1040.580933380327</v>
+        <v>1069.74047276018</v>
       </c>
       <c r="N63" s="183" t="n">
-        <v>1020.642455539125</v>
+        <v>1071.415822172962</v>
       </c>
       <c r="O63" s="183" t="n">
-        <v>1002.362121288176</v>
+        <v>1074.575716800826</v>
       </c>
       <c r="P63" s="183" t="n">
-        <v>39.13923424205985</v>
+        <v>42.9781024117449</v>
       </c>
       <c r="Q63" s="184" t="n">
         <v>0</v>
@@ -6996,46 +6996,46 @@
         </is>
       </c>
       <c r="T63" s="185" t="n">
-        <v>0.007380179040990979</v>
+        <v>0.007586989116471658</v>
       </c>
       <c r="U63" s="186" t="n">
-        <v>0.006769194198737723</v>
+        <v>0.007105937763541331</v>
       </c>
       <c r="V63" s="186" t="n">
-        <v>0.006218861149030665</v>
+        <v>0.006666889176055764</v>
       </c>
       <c r="W63" s="186" t="n">
-        <v>0.000223660413374397</v>
+        <v>0.0002455975528802818</v>
       </c>
       <c r="X63" s="187" t="n">
         <v>0</v>
       </c>
       <c r="Y63" s="185" t="n">
-        <v>0.007324713056696784</v>
+        <v>0.0075299688440857</v>
       </c>
       <c r="Z63" s="186" t="n">
-        <v>0.006731216492670291</v>
+        <v>0.007066070800385279</v>
       </c>
       <c r="AA63" s="186" t="n">
-        <v>0.0061951038111323</v>
+        <v>0.006641420278279971</v>
       </c>
       <c r="AB63" s="186" t="n">
-        <v>0.000223195695006671</v>
+        <v>0.0002450872538417972</v>
       </c>
       <c r="AC63" s="187" t="n">
         <v>0</v>
       </c>
       <c r="AD63" s="188" t="n">
-        <v>1040.580933380327</v>
+        <v>1069.74047276018</v>
       </c>
       <c r="AE63" s="189" t="n">
-        <v>1020.642455539125</v>
+        <v>1071.415822172962</v>
       </c>
       <c r="AF63" s="189" t="n">
-        <v>1002.362121288176</v>
+        <v>1074.575716800826</v>
       </c>
       <c r="AG63" s="189" t="n">
-        <v>39.13923424205985</v>
+        <v>42.9781024117449</v>
       </c>
       <c r="AH63" s="190" t="n">
         <v>0</v>
@@ -7297,49 +7297,49 @@
         </is>
       </c>
       <c r="C68" s="148" t="n">
-        <v>0.003828059914953592</v>
+        <v>0.003935331209533162</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>0.005537928342499777</v>
+        <v>0.00581342076847096</v>
       </c>
       <c r="E68" s="149" t="n">
-        <v>0.007285441474027152</v>
+        <v>0.007810309595600181</v>
       </c>
       <c r="F68" s="149" t="n">
-        <v>0.008863885829097012</v>
+        <v>0.009733276603545954</v>
       </c>
       <c r="G68" s="150" t="n">
-        <v>0.0102542697994211</v>
+        <v>0.01149456660687358</v>
       </c>
       <c r="H68" s="148" t="n">
-        <v>0.003795632420310159</v>
+        <v>0.003901995019778458</v>
       </c>
       <c r="I68" s="149" t="n">
-        <v>0.005503046261004461</v>
+        <v>0.005776803426304191</v>
       </c>
       <c r="J68" s="149" t="n">
-        <v>0.007254274452964378</v>
+        <v>0.007776897195742098</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>0.008843775572310185</v>
+        <v>0.009711193885464006</v>
       </c>
       <c r="L68" s="150" t="n">
-        <v>0.01025181320456335</v>
+        <v>0.01149181287659625</v>
       </c>
       <c r="M68" s="151" t="n">
-        <v>441.6661649120336</v>
+        <v>454.0426956703518</v>
       </c>
       <c r="N68" s="152" t="n">
-        <v>684.1263560477098</v>
+        <v>718.1592322140589</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>960.0887206481668</v>
+        <v>1029.256795794546</v>
       </c>
       <c r="P68" s="152" t="n">
-        <v>1259.318737669335</v>
+        <v>1382.835682012913</v>
       </c>
       <c r="Q68" s="153" t="n">
-        <v>1602.087031014247</v>
+        <v>1795.866156071027</v>
       </c>
       <c r="S68" s="21" t="inlineStr">
         <is>
@@ -7347,49 +7347,49 @@
         </is>
       </c>
       <c r="T68" s="148" t="n">
-        <v>0.004697439758882981</v>
+        <v>0.004829073133318039</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>0.006795631561638907</v>
+        <v>0.007133690292113049</v>
       </c>
       <c r="V68" s="149" t="n">
-        <v>0.008940017450464868</v>
+        <v>0.009584086884387839</v>
       </c>
       <c r="W68" s="149" t="n">
-        <v>0.01087693783191597</v>
+        <v>0.01194377348251524</v>
       </c>
       <c r="X68" s="150" t="n">
-        <v>0.01258308796734119</v>
+        <v>0.01410506506947166</v>
       </c>
       <c r="Y68" s="148" t="n">
-        <v>0.004658094123808976</v>
+        <v>0.004788624940472157</v>
       </c>
       <c r="Z68" s="149" t="n">
-        <v>0.006753308713825994</v>
+        <v>0.007089262031716786</v>
       </c>
       <c r="AA68" s="149" t="n">
-        <v>0.008902202994527524</v>
+        <v>0.009543548145711159</v>
       </c>
       <c r="AB68" s="149" t="n">
-        <v>0.01085253892857899</v>
+        <v>0.01191698147734045</v>
       </c>
       <c r="AC68" s="150" t="n">
-        <v>0.01258010755564418</v>
+        <v>0.01410172416451818</v>
       </c>
       <c r="AD68" s="151" t="n">
-        <v>441.6661649120336</v>
+        <v>454.0426956703518</v>
       </c>
       <c r="AE68" s="152" t="n">
-        <v>684.1263560477098</v>
+        <v>718.1592322140589</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>960.0887206481668</v>
+        <v>1029.256795794546</v>
       </c>
       <c r="AG68" s="152" t="n">
-        <v>1259.318737669335</v>
+        <v>1382.835682012913</v>
       </c>
       <c r="AH68" s="153" t="n">
-        <v>1602.087031014247</v>
+        <v>1795.866156071027</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -7501,49 +7501,49 @@
         </is>
       </c>
       <c r="C70" s="161" t="n">
-        <v>0.003129897296122921</v>
+        <v>0.003217604422530391</v>
       </c>
       <c r="D70" s="162" t="n">
-        <v>0.004560299655573442</v>
+        <v>0.004787158498369949</v>
       </c>
       <c r="E70" s="162" t="n">
-        <v>0.00602285708723745</v>
+        <v>0.00645676431127472</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>0.007338043010000024</v>
+        <v>0.008057775531199868</v>
       </c>
       <c r="G70" s="163" t="n">
-        <v>0.008499339546816751</v>
+        <v>0.009527370202492159</v>
       </c>
       <c r="H70" s="161" t="n">
-        <v>0.003103132937333462</v>
+        <v>0.003190090063093157</v>
       </c>
       <c r="I70" s="162" t="n">
-        <v>0.004530931271734024</v>
+        <v>0.004756329140893751</v>
       </c>
       <c r="J70" s="162" t="n">
-        <v>0.005996119373436025</v>
+        <v>0.006428100321122281</v>
       </c>
       <c r="K70" s="162" t="n">
-        <v>0.007320260527053694</v>
+        <v>0.008038248900492791</v>
       </c>
       <c r="L70" s="163" t="n">
-        <v>0.008496087095796462</v>
+        <v>0.009523724353921799</v>
       </c>
       <c r="M70" s="164" t="n">
-        <v>441.6661649120336</v>
+        <v>454.0426956703518</v>
       </c>
       <c r="N70" s="165" t="n">
-        <v>684.1263560477098</v>
+        <v>718.1592322140589</v>
       </c>
       <c r="O70" s="165" t="n">
-        <v>960.0887206481668</v>
+        <v>1029.256795794546</v>
       </c>
       <c r="P70" s="165" t="n">
-        <v>1259.318737669335</v>
+        <v>1382.835682012913</v>
       </c>
       <c r="Q70" s="166" t="n">
-        <v>1602.087031014247</v>
+        <v>1795.866156071027</v>
       </c>
       <c r="S70" s="42" t="inlineStr">
         <is>
@@ -7551,49 +7551,49 @@
         </is>
       </c>
       <c r="T70" s="161" t="n">
-        <v>0.003697070544212643</v>
+        <v>0.003800671206752036</v>
       </c>
       <c r="U70" s="162" t="n">
-        <v>0.005393144949219606</v>
+        <v>0.005661434911419455</v>
       </c>
       <c r="V70" s="162" t="n">
-        <v>0.007127536728527655</v>
+        <v>0.007641028852166551</v>
       </c>
       <c r="W70" s="162" t="n">
-        <v>0.008686018566347624</v>
+        <v>0.009537963701232572</v>
       </c>
       <c r="X70" s="163" t="n">
-        <v>0.01006270981792341</v>
+        <v>0.01127983664466203</v>
       </c>
       <c r="Y70" s="161" t="n">
-        <v>0.003665626347905138</v>
+        <v>0.00376834586967875</v>
       </c>
       <c r="Z70" s="162" t="n">
-        <v>0.005358523374732888</v>
+        <v>0.005625091035567246</v>
       </c>
       <c r="AA70" s="162" t="n">
-        <v>0.007095912368644929</v>
+        <v>0.007607126165235729</v>
       </c>
       <c r="AB70" s="162" t="n">
-        <v>0.00866487377985147</v>
+        <v>0.009514744984333669</v>
       </c>
       <c r="AC70" s="163" t="n">
-        <v>0.01005861799473526</v>
+        <v>0.01127524989835053</v>
       </c>
       <c r="AD70" s="164" t="n">
-        <v>441.6661649120336</v>
+        <v>454.0426956703518</v>
       </c>
       <c r="AE70" s="165" t="n">
-        <v>684.1263560477098</v>
+        <v>718.1592322140589</v>
       </c>
       <c r="AF70" s="165" t="n">
-        <v>960.0887206481668</v>
+        <v>1029.256795794546</v>
       </c>
       <c r="AG70" s="165" t="n">
-        <v>1259.318737669335</v>
+        <v>1382.835682012913</v>
       </c>
       <c r="AH70" s="166" t="n">
-        <v>1602.087031014247</v>
+        <v>1795.866156071027</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" thickBot="1">
@@ -7603,49 +7603,49 @@
         </is>
       </c>
       <c r="C71" s="155" t="n">
-        <v>0.008690064678311177</v>
+        <v>0.008829475055652746</v>
       </c>
       <c r="D71" s="156" t="n">
-        <v>0.01266890429561433</v>
+        <v>0.0130201614973281</v>
       </c>
       <c r="E71" s="156" t="n">
-        <v>0.01662674882489198</v>
+        <v>0.01726845000666726</v>
       </c>
       <c r="F71" s="156" t="n">
-        <v>0.02013203964405095</v>
+        <v>0.02113694321030984</v>
       </c>
       <c r="G71" s="157" t="n">
-        <v>0.0230512031623378</v>
+        <v>0.02445839321279067</v>
       </c>
       <c r="H71" s="155" t="n">
-        <v>0.008652558177116375</v>
+        <v>0.00879136685634891</v>
       </c>
       <c r="I71" s="156" t="n">
-        <v>0.01263655807645514</v>
+        <v>0.01298691844903809</v>
       </c>
       <c r="J71" s="156" t="n">
-        <v>0.01661295288206362</v>
+        <v>0.01725412161622032</v>
       </c>
       <c r="K71" s="156" t="n">
-        <v>0.02013203964405095</v>
+        <v>0.02113694321030984</v>
       </c>
       <c r="L71" s="157" t="n">
-        <v>0.0230512031623378</v>
+        <v>0.02445839321279067</v>
       </c>
       <c r="M71" s="158" t="n">
-        <v>74.60263068385404</v>
+        <v>75.79944351313796</v>
       </c>
       <c r="N71" s="159" t="n">
-        <v>117.1463995275705</v>
+        <v>120.3943928448097</v>
       </c>
       <c r="O71" s="159" t="n">
-        <v>166.9582110181674</v>
+        <v>173.4018809409997</v>
       </c>
       <c r="P71" s="159" t="n">
-        <v>223.4715256823137</v>
+        <v>234.6262490529202</v>
       </c>
       <c r="Q71" s="160" t="n">
-        <v>288.7970884033706</v>
+        <v>306.4270744192399</v>
       </c>
       <c r="S71" s="32" t="inlineStr">
         <is>
@@ -7653,49 +7653,49 @@
         </is>
       </c>
       <c r="T71" s="155" t="n">
-        <v>0.01057465574841193</v>
+        <v>0.01074429968119217</v>
       </c>
       <c r="U71" s="156" t="n">
-        <v>0.01541637566519635</v>
+        <v>0.01584380907619778</v>
       </c>
       <c r="V71" s="156" t="n">
-        <v>0.02023254734540302</v>
+        <v>0.02101341254512458</v>
       </c>
       <c r="W71" s="156" t="n">
-        <v>0.02449802120351918</v>
+        <v>0.02572085551683114</v>
       </c>
       <c r="X71" s="157" t="n">
-        <v>0.02805025590163947</v>
+        <v>0.02976261949235803</v>
       </c>
       <c r="Y71" s="155" t="n">
-        <v>0.01052563708375766</v>
+        <v>0.01069449463452703</v>
       </c>
       <c r="Z71" s="156" t="n">
-        <v>0.01537409562759671</v>
+        <v>0.01580035678507495</v>
       </c>
       <c r="AA71" s="156" t="n">
-        <v>0.0202145122319452</v>
+        <v>0.02099468137534563</v>
       </c>
       <c r="AB71" s="156" t="n">
-        <v>0.02449802120351918</v>
+        <v>0.02572085551683114</v>
       </c>
       <c r="AC71" s="157" t="n">
-        <v>0.02805025590163947</v>
+        <v>0.02976261949235803</v>
       </c>
       <c r="AD71" s="158" t="n">
-        <v>74.60263068385404</v>
+        <v>75.79944351313796</v>
       </c>
       <c r="AE71" s="159" t="n">
-        <v>117.1463995275705</v>
+        <v>120.3943928448097</v>
       </c>
       <c r="AF71" s="159" t="n">
-        <v>166.9582110181674</v>
+        <v>173.4018809409997</v>
       </c>
       <c r="AG71" s="159" t="n">
-        <v>223.4715256823137</v>
+        <v>234.6262490529202</v>
       </c>
       <c r="AH71" s="160" t="n">
-        <v>288.7970884033706</v>
+        <v>306.4270744192399</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" thickTop="1">
@@ -7705,49 +7705,49 @@
         </is>
       </c>
       <c r="C72" s="161" t="n">
-        <v>0.003448761918252369</v>
+        <v>0.003539434124025035</v>
       </c>
       <c r="D72" s="162" t="n">
-        <v>0.005031078253823111</v>
+        <v>0.005265159558144803</v>
       </c>
       <c r="E72" s="162" t="n">
-        <v>0.006651243167789535</v>
+        <v>0.007097464251105633</v>
       </c>
       <c r="F72" s="162" t="n">
-        <v>0.00811530171464012</v>
+        <v>0.008852358898603554</v>
       </c>
       <c r="G72" s="163" t="n">
-        <v>0.009406261608399682</v>
+        <v>0.01045792277828726</v>
       </c>
       <c r="H72" s="161" t="n">
-        <v>0.003420105158043028</v>
+        <v>0.003510023942234248</v>
       </c>
       <c r="I72" s="162" t="n">
-        <v>0.004999809220640237</v>
+        <v>0.005232435668626358</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>0.006623133721044964</v>
+        <v>0.00706746898730982</v>
       </c>
       <c r="K72" s="162" t="n">
-        <v>0.008096827707005544</v>
+        <v>0.008832207023586785</v>
       </c>
       <c r="L72" s="163" t="n">
-        <v>0.009402886357508551</v>
+        <v>0.01045417015959066</v>
       </c>
       <c r="M72" s="164" t="n">
-        <v>516.2687955958877</v>
+        <v>529.8421391834897</v>
       </c>
       <c r="N72" s="165" t="n">
-        <v>801.2727555752804</v>
+        <v>838.5536250588686</v>
       </c>
       <c r="O72" s="165" t="n">
-        <v>1127.046931666334</v>
+        <v>1202.658676735546</v>
       </c>
       <c r="P72" s="165" t="n">
-        <v>1482.790263351648</v>
+        <v>1617.461931065833</v>
       </c>
       <c r="Q72" s="166" t="n">
-        <v>1890.884119417617</v>
+        <v>2102.293230490267</v>
       </c>
       <c r="S72" s="42" t="inlineStr">
         <is>
@@ -7755,49 +7755,49 @@
         </is>
       </c>
       <c r="T72" s="161" t="n">
-        <v>0.004080573984018177</v>
+        <v>0.004187857308503786</v>
       </c>
       <c r="U72" s="162" t="n">
-        <v>0.005959636998583706</v>
+        <v>0.006236921415865865</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>0.007884021892021234</v>
+        <v>0.008412948094356238</v>
       </c>
       <c r="W72" s="162" t="n">
-        <v>0.009621991545811469</v>
+        <v>0.01049589103128368</v>
       </c>
       <c r="X72" s="163" t="n">
-        <v>0.01115526360096161</v>
+        <v>0.01240247083986249</v>
       </c>
       <c r="Y72" s="161" t="n">
-        <v>0.004046745295008114</v>
+        <v>0.004153139221523193</v>
       </c>
       <c r="Z72" s="162" t="n">
-        <v>0.00592261300340978</v>
+        <v>0.006198174802866441</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>0.007850649254318403</v>
+        <v>0.008377336540683383</v>
       </c>
       <c r="AB72" s="162" t="n">
-        <v>0.009599951613061569</v>
+        <v>0.01047184936263553</v>
       </c>
       <c r="AC72" s="163" t="n">
-        <v>0.01115100292454234</v>
+        <v>0.01239773380119283</v>
       </c>
       <c r="AD72" s="164" t="n">
-        <v>516.2687955958877</v>
+        <v>529.8421391834897</v>
       </c>
       <c r="AE72" s="165" t="n">
-        <v>801.2727555752804</v>
+        <v>838.5536250588686</v>
       </c>
       <c r="AF72" s="165" t="n">
-        <v>1127.046931666334</v>
+        <v>1202.658676735546</v>
       </c>
       <c r="AG72" s="165" t="n">
-        <v>1482.790263351648</v>
+        <v>1617.461931065833</v>
       </c>
       <c r="AH72" s="166" t="n">
-        <v>1890.884119417617</v>
+        <v>2102.293230490267</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" thickBot="1">
@@ -7909,49 +7909,49 @@
         </is>
       </c>
       <c r="C74" s="179" t="n">
-        <v>0.003247358839010462</v>
+        <v>0.003332735909346952</v>
       </c>
       <c r="D74" s="180" t="n">
-        <v>0.004720728559740944</v>
+        <v>0.004940370203711223</v>
       </c>
       <c r="E74" s="180" t="n">
-        <v>0.006222039120725584</v>
+        <v>0.006639465602789991</v>
       </c>
       <c r="F74" s="180" t="n">
-        <v>0.007560965041182681</v>
+        <v>0.008247675627832412</v>
       </c>
       <c r="G74" s="181" t="n">
-        <v>0.008737437082737052</v>
+        <v>0.009714320746704556</v>
       </c>
       <c r="H74" s="179" t="n">
-        <v>0.003221764706680653</v>
+        <v>0.003306468875701196</v>
       </c>
       <c r="I74" s="180" t="n">
-        <v>0.004692945950680881</v>
+        <v>0.004911294951396941</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>0.006197127641346853</v>
+        <v>0.006612882852787866</v>
       </c>
       <c r="K74" s="180" t="n">
-        <v>0.00754457678568891</v>
+        <v>0.008229798939515186</v>
       </c>
       <c r="L74" s="181" t="n">
-        <v>0.008734152604133712</v>
+        <v>0.009710669049034356</v>
       </c>
       <c r="M74" s="182" t="n">
-        <v>516.2687955958877</v>
+        <v>529.8421391834897</v>
       </c>
       <c r="N74" s="183" t="n">
-        <v>801.2727555752804</v>
+        <v>838.5536250588686</v>
       </c>
       <c r="O74" s="183" t="n">
-        <v>1127.046931666334</v>
+        <v>1202.658676735546</v>
       </c>
       <c r="P74" s="183" t="n">
-        <v>1482.790263351648</v>
+        <v>1617.461931065833</v>
       </c>
       <c r="Q74" s="184" t="n">
-        <v>1890.884119417617</v>
+        <v>2102.293230490267</v>
       </c>
       <c r="S74" s="51" t="inlineStr">
         <is>
@@ -7959,49 +7959,49 @@
         </is>
       </c>
       <c r="T74" s="185" t="n">
-        <v>0.003661566364085816</v>
+        <v>0.003757833461288889</v>
       </c>
       <c r="U74" s="186" t="n">
-        <v>0.005314271280025993</v>
+        <v>0.00556152872465081</v>
       </c>
       <c r="V74" s="186" t="n">
-        <v>0.006992431405395187</v>
+        <v>0.007461542252498062</v>
       </c>
       <c r="W74" s="186" t="n">
-        <v>0.008473376898426175</v>
+        <v>0.009242955594945628</v>
       </c>
       <c r="X74" s="187" t="n">
-        <v>0.009771914713709947</v>
+        <v>0.01086445749932467</v>
       </c>
       <c r="Y74" s="185" t="n">
-        <v>0.003634047738681944</v>
+        <v>0.003729591337271792</v>
       </c>
       <c r="Z74" s="186" t="n">
-        <v>0.005284456234584829</v>
+        <v>0.005530326472656067</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>0.006965718868863477</v>
+        <v>0.007433037615348677</v>
       </c>
       <c r="AB74" s="186" t="n">
-        <v>0.008455771038623118</v>
+        <v>0.009223750715672437</v>
       </c>
       <c r="AC74" s="187" t="n">
-        <v>0.009768105161425037</v>
+        <v>0.0108602220224398</v>
       </c>
       <c r="AD74" s="188" t="n">
-        <v>516.2687955958877</v>
+        <v>529.8421391834897</v>
       </c>
       <c r="AE74" s="189" t="n">
-        <v>801.2727555752804</v>
+        <v>838.5536250588686</v>
       </c>
       <c r="AF74" s="189" t="n">
-        <v>1127.046931666334</v>
+        <v>1202.658676735546</v>
       </c>
       <c r="AG74" s="189" t="n">
-        <v>1482.790263351648</v>
+        <v>1617.461931065833</v>
       </c>
       <c r="AH74" s="190" t="n">
-        <v>1890.884119417617</v>
+        <v>2102.293230490267</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" thickBot="1"/>
@@ -8260,49 +8260,49 @@
         </is>
       </c>
       <c r="C79" s="148" t="n">
-        <v>471.5678719674212</v>
+        <v>460.8781434746102</v>
       </c>
       <c r="D79" s="149" t="n">
-        <v>512.5515548986774</v>
+        <v>493.6282105350419</v>
       </c>
       <c r="E79" s="149" t="n">
-        <v>550.8261298256524</v>
+        <v>524.044898931777</v>
       </c>
       <c r="F79" s="149" t="n">
-        <v>587.5580120830728</v>
+        <v>552.5622721513189</v>
       </c>
       <c r="G79" s="150" t="n">
-        <v>621.4696511966528</v>
+        <v>578.5638182258624</v>
       </c>
       <c r="H79" s="148" t="n">
-        <v>467.5732206343781</v>
+        <v>456.9740448291272</v>
       </c>
       <c r="I79" s="149" t="n">
-        <v>509.3231156696397</v>
+        <v>490.5189649104412</v>
       </c>
       <c r="J79" s="149" t="n">
-        <v>548.4697030186559</v>
+        <v>521.803041871903</v>
       </c>
       <c r="K79" s="149" t="n">
-        <v>586.22496890901</v>
+        <v>551.3086268090922</v>
       </c>
       <c r="L79" s="150" t="n">
-        <v>621.3207669582583</v>
+        <v>578.4252128518538</v>
       </c>
       <c r="M79" s="151" t="n">
-        <v>54407605.45413375</v>
+        <v>53174267.5513157</v>
       </c>
       <c r="N79" s="152" t="n">
-        <v>63317906.23732398</v>
+        <v>60980216.43292934</v>
       </c>
       <c r="O79" s="152" t="n">
-        <v>72588868.65939853</v>
+        <v>69059589.37029169</v>
       </c>
       <c r="P79" s="152" t="n">
-        <v>83476121.9120234</v>
+        <v>78504172.60171169</v>
       </c>
       <c r="Q79" s="153" t="n">
-        <v>97095989.06860377</v>
+        <v>90392549.43790017</v>
       </c>
       <c r="S79" s="21" t="inlineStr">
         <is>
@@ -8310,49 +8310,49 @@
         </is>
       </c>
       <c r="T79" s="148" t="n">
-        <v>578.6643156076251</v>
+        <v>565.5468731565177</v>
       </c>
       <c r="U79" s="149" t="n">
-        <v>628.9556866790913</v>
+        <v>605.7347151792623</v>
       </c>
       <c r="V79" s="149" t="n">
-        <v>675.9226919012386</v>
+        <v>643.0592515195223</v>
       </c>
       <c r="W79" s="149" t="n">
-        <v>720.996647891477</v>
+        <v>678.0531245926934</v>
       </c>
       <c r="X79" s="150" t="n">
-        <v>762.6098633060934</v>
+        <v>709.9598081442932</v>
       </c>
       <c r="Y79" s="148" t="n">
-        <v>573.817438125228</v>
+        <v>560.8098670360279</v>
       </c>
       <c r="Z79" s="149" t="n">
-        <v>625.0385826443979</v>
+        <v>601.9622301743001</v>
       </c>
       <c r="AA79" s="149" t="n">
-        <v>673.0636763577487</v>
+        <v>640.3392416463399</v>
       </c>
       <c r="AB79" s="149" t="n">
-        <v>719.3793243588769</v>
+        <v>676.5321310097637</v>
       </c>
       <c r="AC79" s="150" t="n">
-        <v>762.429232656228</v>
+        <v>709.7916481090067</v>
       </c>
       <c r="AD79" s="151" t="n">
-        <v>54407605.45413375</v>
+        <v>53174267.5513157</v>
       </c>
       <c r="AE79" s="152" t="n">
-        <v>63317906.23732398</v>
+        <v>60980216.43292934</v>
       </c>
       <c r="AF79" s="152" t="n">
-        <v>72588868.65939853</v>
+        <v>69059589.37029169</v>
       </c>
       <c r="AG79" s="152" t="n">
-        <v>83476121.9120234</v>
+        <v>78504172.60171169</v>
       </c>
       <c r="AH79" s="153" t="n">
-        <v>97095989.06860377</v>
+        <v>90392549.43790017</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" thickBot="1">
@@ -8362,49 +8362,49 @@
         </is>
       </c>
       <c r="C80" s="155" t="n">
-        <v>1046.529579090464</v>
+        <v>1029.220716820228</v>
       </c>
       <c r="D80" s="156" t="n">
-        <v>1126.574450002636</v>
+        <v>1095.363081260288</v>
       </c>
       <c r="E80" s="156" t="n">
-        <v>1204.017802653421</v>
+        <v>1159.517628447959</v>
       </c>
       <c r="F80" s="156" t="n">
-        <v>1272.632962688617</v>
+        <v>1214.312887632912</v>
       </c>
       <c r="G80" s="157" t="n">
-        <v>1334.413639823041</v>
+        <v>1262.062596963041</v>
       </c>
       <c r="H80" s="155" t="n">
-        <v>1037.204426015099</v>
+        <v>1020.04979520994</v>
       </c>
       <c r="I80" s="156" t="n">
-        <v>1118.577604657871</v>
+        <v>1087.587785844009</v>
       </c>
       <c r="J80" s="156" t="n">
-        <v>1197.746659998266</v>
+        <v>1153.478265538923</v>
       </c>
       <c r="K80" s="156" t="n">
-        <v>1268.603960540155</v>
+        <v>1210.468519793467</v>
       </c>
       <c r="L80" s="157" t="n">
-        <v>1332.978935541728</v>
+        <v>1260.705681418182</v>
       </c>
       <c r="M80" s="158" t="n">
-        <v>26933538.63435648</v>
+        <v>26488076.8719882</v>
       </c>
       <c r="N80" s="159" t="n">
-        <v>29835233.6544558</v>
+        <v>29008658.47418153</v>
       </c>
       <c r="O80" s="159" t="n">
-        <v>33261839.11560193</v>
+        <v>32032490.48655647</v>
       </c>
       <c r="P80" s="159" t="n">
-        <v>37596223.68710625</v>
+        <v>35873327.41494709</v>
       </c>
       <c r="Q80" s="160" t="n">
-        <v>43047359.62179434</v>
+        <v>40713359.67750474</v>
       </c>
       <c r="S80" s="32" t="inlineStr">
         <is>
@@ -8412,49 +8412,49 @@
         </is>
       </c>
       <c r="T80" s="155" t="n">
-        <v>1058.663462971984</v>
+        <v>1041.153914807049</v>
       </c>
       <c r="U80" s="156" t="n">
-        <v>1139.636406237165</v>
+        <v>1108.063160361414</v>
       </c>
       <c r="V80" s="156" t="n">
-        <v>1217.977668194323</v>
+        <v>1172.961541112512</v>
       </c>
       <c r="W80" s="156" t="n">
-        <v>1287.388379928213</v>
+        <v>1228.392118520182</v>
       </c>
       <c r="X80" s="157" t="n">
-        <v>1349.885367024102</v>
+        <v>1276.695457140838</v>
       </c>
       <c r="Y80" s="155" t="n">
-        <v>1049.15420339551</v>
+        <v>1031.801931687533</v>
       </c>
       <c r="Z80" s="156" t="n">
-        <v>1131.481559061162</v>
+        <v>1100.134240501841</v>
       </c>
       <c r="AA80" s="156" t="n">
-        <v>1211.582521945054</v>
+        <v>1166.802757748854</v>
       </c>
       <c r="AB80" s="156" t="n">
-        <v>1283.279641349469</v>
+        <v>1224.471668276976</v>
       </c>
       <c r="AC80" s="157" t="n">
-        <v>1348.422244199315</v>
+        <v>1275.311663887516</v>
       </c>
       <c r="AD80" s="158" t="n">
-        <v>26933538.63435648</v>
+        <v>26488076.8719882</v>
       </c>
       <c r="AE80" s="159" t="n">
-        <v>29835233.6544558</v>
+        <v>29008658.47418153</v>
       </c>
       <c r="AF80" s="159" t="n">
-        <v>33261839.11560193</v>
+        <v>32032490.48655647</v>
       </c>
       <c r="AG80" s="159" t="n">
-        <v>37596223.68710625</v>
+        <v>35873327.41494709</v>
       </c>
       <c r="AH80" s="160" t="n">
-        <v>43047359.62179434</v>
+        <v>40713359.67750474</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" thickTop="1">
@@ -8464,49 +8464,49 @@
         </is>
       </c>
       <c r="C81" s="161" t="n">
-        <v>576.4295460505039</v>
+        <v>564.532618121136</v>
       </c>
       <c r="D81" s="162" t="n">
-        <v>620.9470341388846</v>
+        <v>599.854444455463</v>
       </c>
       <c r="E81" s="162" t="n">
-        <v>664.0258049082821</v>
+        <v>634.1738388701635</v>
       </c>
       <c r="F81" s="162" t="n">
-        <v>705.4878584370598</v>
+        <v>666.4770319004825</v>
       </c>
       <c r="G81" s="163" t="n">
-        <v>743.4838948752704</v>
+        <v>695.5387669922499</v>
       </c>
       <c r="H81" s="161" t="n">
-        <v>571.5003852098425</v>
+        <v>559.7051902184813</v>
       </c>
       <c r="I81" s="162" t="n">
-        <v>616.9481278783604</v>
+        <v>595.9913747225303</v>
       </c>
       <c r="J81" s="162" t="n">
-        <v>661.0779461642948</v>
+        <v>631.358504161327</v>
       </c>
       <c r="K81" s="162" t="n">
-        <v>703.7782301622727</v>
+        <v>664.8619396425413</v>
       </c>
       <c r="L81" s="163" t="n">
-        <v>743.1993851272911</v>
+        <v>695.2726044557501</v>
       </c>
       <c r="M81" s="164" t="n">
-        <v>81341144.08849022</v>
+        <v>79662344.4233039</v>
       </c>
       <c r="N81" s="165" t="n">
-        <v>93153139.89177978</v>
+        <v>89988874.90711087</v>
       </c>
       <c r="O81" s="165" t="n">
-        <v>105850707.7750005</v>
+        <v>101092079.8568482</v>
       </c>
       <c r="P81" s="165" t="n">
-        <v>121072345.5991296</v>
+        <v>114377500.0166588</v>
       </c>
       <c r="Q81" s="166" t="n">
-        <v>140143348.6903981</v>
+        <v>131105909.1154049</v>
       </c>
       <c r="S81" s="42" t="inlineStr">
         <is>
@@ -8514,49 +8514,49 @@
         </is>
       </c>
       <c r="T81" s="161" t="n">
-        <v>680.8851837269639</v>
+        <v>666.8323961582566</v>
       </c>
       <c r="U81" s="162" t="n">
-        <v>734.3502870049692</v>
+        <v>709.4055679933405</v>
       </c>
       <c r="V81" s="162" t="n">
-        <v>785.8178011898968</v>
+        <v>750.4905501405046</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>835.0837721128464</v>
+        <v>788.9067787205337</v>
       </c>
       <c r="X81" s="163" t="n">
-        <v>880.2404760063199</v>
+        <v>823.4763114012292</v>
       </c>
       <c r="Y81" s="161" t="n">
-        <v>675.0941426516193</v>
+        <v>661.1608763648821</v>
       </c>
       <c r="Z81" s="162" t="n">
-        <v>729.6360871456527</v>
+        <v>704.8515020550371</v>
       </c>
       <c r="AA81" s="162" t="n">
-        <v>782.3311850006577</v>
+        <v>747.1606783839363</v>
       </c>
       <c r="AB81" s="162" t="n">
-        <v>833.0508881243018</v>
+        <v>786.9863055746388</v>
       </c>
       <c r="AC81" s="163" t="n">
-        <v>879.8825417663351</v>
+        <v>823.1414593060334</v>
       </c>
       <c r="AD81" s="164" t="n">
-        <v>81341144.08849022</v>
+        <v>79662344.4233039</v>
       </c>
       <c r="AE81" s="165" t="n">
-        <v>93153139.89177978</v>
+        <v>89988874.90711087</v>
       </c>
       <c r="AF81" s="165" t="n">
-        <v>105850707.7750005</v>
+        <v>101092079.8568482</v>
       </c>
       <c r="AG81" s="165" t="n">
-        <v>121072345.5991296</v>
+        <v>114377500.0166588</v>
       </c>
       <c r="AH81" s="166" t="n">
-        <v>140143348.6903981</v>
+        <v>131105909.1154049</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" thickBot="1">
@@ -8566,49 +8566,49 @@
         </is>
       </c>
       <c r="C82" s="155" t="n">
-        <v>1213.105812026243</v>
+        <v>1192.609081967945</v>
       </c>
       <c r="D82" s="156" t="n">
-        <v>1295.392884503767</v>
+        <v>1259.453427554498</v>
       </c>
       <c r="E82" s="156" t="n">
-        <v>1366.719122978157</v>
+        <v>1316.223157963662</v>
       </c>
       <c r="F82" s="156" t="n">
-        <v>1425.325714617607</v>
+        <v>1360.063968947291</v>
       </c>
       <c r="G82" s="157" t="n">
-        <v>1465.925862055849</v>
+        <v>1386.480554818694</v>
       </c>
       <c r="H82" s="155" t="n">
-        <v>1207.870021928875</v>
+        <v>1187.461756186883</v>
       </c>
       <c r="I82" s="156" t="n">
-        <v>1292.085490181282</v>
+        <v>1256.237793776084</v>
       </c>
       <c r="J82" s="156" t="n">
-        <v>1365.585096171016</v>
+        <v>1315.131029873686</v>
       </c>
       <c r="K82" s="156" t="n">
-        <v>1425.325714617606</v>
+        <v>1360.06396894729</v>
       </c>
       <c r="L82" s="157" t="n">
-        <v>1465.925862055849</v>
+        <v>1386.480554818694</v>
       </c>
       <c r="M82" s="158" t="n">
-        <v>10414293.58988598</v>
+        <v>10238332.87620082</v>
       </c>
       <c r="N82" s="159" t="n">
-        <v>11978195.4975998</v>
+        <v>11645871.73191784</v>
       </c>
       <c r="O82" s="159" t="n">
-        <v>13723968.6567668</v>
+        <v>13216911.25960239</v>
       </c>
       <c r="P82" s="159" t="n">
-        <v>15821532.12846238</v>
+        <v>15097107.67214823</v>
       </c>
       <c r="Q82" s="160" t="n">
-        <v>18365857.85980269</v>
+        <v>17370527.01933324</v>
       </c>
       <c r="S82" s="32" t="inlineStr">
         <is>
@@ -8616,49 +8616,49 @@
         </is>
       </c>
       <c r="T82" s="155" t="n">
-        <v>1476.188822920045</v>
+        <v>1451.247021868139</v>
       </c>
       <c r="U82" s="156" t="n">
-        <v>1576.321272585948</v>
+        <v>1532.587721790646</v>
       </c>
       <c r="V82" s="156" t="n">
-        <v>1663.115841512263</v>
+        <v>1601.668951704313</v>
       </c>
       <c r="W82" s="156" t="n">
-        <v>1734.43228783535</v>
+        <v>1655.0174020375</v>
       </c>
       <c r="X82" s="157" t="n">
-        <v>1783.837280592852</v>
+        <v>1687.162882189755</v>
       </c>
       <c r="Y82" s="155" t="n">
-        <v>1469.345970859544</v>
+        <v>1444.519787167742</v>
       </c>
       <c r="Z82" s="156" t="n">
-        <v>1571.998147350716</v>
+        <v>1528.384537598116</v>
       </c>
       <c r="AA82" s="156" t="n">
-        <v>1661.633354785154</v>
+        <v>1600.241238190403</v>
       </c>
       <c r="AB82" s="156" t="n">
-        <v>1734.43228783535</v>
+        <v>1655.0174020375</v>
       </c>
       <c r="AC82" s="157" t="n">
-        <v>1783.837280592852</v>
+        <v>1687.162882189755</v>
       </c>
       <c r="AD82" s="158" t="n">
-        <v>10414293.58988598</v>
+        <v>10238332.87620082</v>
       </c>
       <c r="AE82" s="159" t="n">
-        <v>11978195.4975998</v>
+        <v>11645871.73191784</v>
       </c>
       <c r="AF82" s="159" t="n">
-        <v>13723968.6567668</v>
+        <v>13216911.25960239</v>
       </c>
       <c r="AG82" s="159" t="n">
-        <v>15821532.12846238</v>
+        <v>15097107.67214823</v>
       </c>
       <c r="AH82" s="160" t="n">
-        <v>18365857.85980269</v>
+        <v>17370527.01933324</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" thickTop="1">
@@ -8668,49 +8668,49 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>612.9416729370947</v>
+        <v>600.5515633339136</v>
       </c>
       <c r="D83" s="162" t="n">
-        <v>660.1047790438679</v>
+        <v>638.1501930404753</v>
       </c>
       <c r="E83" s="162" t="n">
-        <v>705.6673748994274</v>
+        <v>674.5920465406979</v>
       </c>
       <c r="F83" s="162" t="n">
-        <v>749.2193252843074</v>
+        <v>708.6137073791597</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>788.5089566515919</v>
+        <v>738.6006295279178</v>
       </c>
       <c r="H83" s="161" t="n">
-        <v>607.8485633052846</v>
+        <v>595.5614067061908</v>
       </c>
       <c r="I83" s="162" t="n">
-        <v>656.0021121405234</v>
+        <v>634.1839777372891</v>
       </c>
       <c r="J83" s="162" t="n">
-        <v>702.6850873790767</v>
+        <v>671.7410893995761</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>747.5137715018394</v>
+        <v>707.0005899005488</v>
       </c>
       <c r="L83" s="163" t="n">
-        <v>788.2260158118191</v>
+        <v>738.3355973039812</v>
       </c>
       <c r="M83" s="164" t="n">
-        <v>91755437.6783762</v>
+        <v>89900677.29950471</v>
       </c>
       <c r="N83" s="165" t="n">
-        <v>105131335.3893796</v>
+        <v>101634746.6390287</v>
       </c>
       <c r="O83" s="165" t="n">
-        <v>119574676.4317673</v>
+        <v>114308991.1164506</v>
       </c>
       <c r="P83" s="165" t="n">
-        <v>136893877.7275921</v>
+        <v>129474607.688807</v>
       </c>
       <c r="Q83" s="166" t="n">
-        <v>158509206.5502008</v>
+        <v>148476436.1347381</v>
       </c>
       <c r="S83" s="42" t="inlineStr">
         <is>
@@ -8718,49 +8718,49 @@
         </is>
       </c>
       <c r="T83" s="161" t="n">
-        <v>725.2323887800077</v>
+        <v>710.5724151128503</v>
       </c>
       <c r="U83" s="162" t="n">
-        <v>781.9367272099826</v>
+        <v>755.9301026986304</v>
       </c>
       <c r="V83" s="162" t="n">
-        <v>836.4597251736333</v>
+        <v>799.6247211147764</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>888.3196543190837</v>
+        <v>840.1751828090545</v>
       </c>
       <c r="X83" s="163" t="n">
-        <v>935.1244553216516</v>
+        <v>875.9361647843733</v>
       </c>
       <c r="Y83" s="161" t="n">
-        <v>719.2200824142485</v>
+        <v>704.6816425538607</v>
       </c>
       <c r="Z83" s="162" t="n">
-        <v>777.0789780515324</v>
+        <v>751.2339186054061</v>
       </c>
       <c r="AA83" s="162" t="n">
-        <v>832.9190364561807</v>
+        <v>796.2399529746732</v>
       </c>
       <c r="AB83" s="162" t="n">
-        <v>886.2848878834254</v>
+        <v>838.2506950936911</v>
       </c>
       <c r="AC83" s="163" t="n">
-        <v>934.7672909498905</v>
+        <v>875.6016069742149</v>
       </c>
       <c r="AD83" s="164" t="n">
-        <v>91755437.6783762</v>
+        <v>89900677.29950471</v>
       </c>
       <c r="AE83" s="165" t="n">
-        <v>105131335.3893796</v>
+        <v>101634746.6390287</v>
       </c>
       <c r="AF83" s="165" t="n">
-        <v>119574676.4317673</v>
+        <v>114308991.1164506</v>
       </c>
       <c r="AG83" s="165" t="n">
-        <v>136893877.7275921</v>
+        <v>129474607.688807</v>
       </c>
       <c r="AH83" s="166" t="n">
-        <v>158509206.5502008</v>
+        <v>148476436.1347381</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" thickBot="1">
@@ -8770,49 +8770,49 @@
         </is>
       </c>
       <c r="C84" s="155" t="n">
-        <v>7036.394727151741</v>
+        <v>6942.06631056527</v>
       </c>
       <c r="D84" s="156" t="n">
-        <v>7312.518501574925</v>
+        <v>7142.221825372106</v>
       </c>
       <c r="E84" s="156" t="n">
-        <v>7747.254145988883</v>
+        <v>7665.143286208036</v>
       </c>
       <c r="F84" s="156" t="n">
-        <v>7954.575400994801</v>
+        <v>7955.939721301899</v>
       </c>
       <c r="G84" s="157" t="n">
-        <v>8276.723507749737</v>
+        <v>8360.61838229466</v>
       </c>
       <c r="H84" s="155" t="n">
-        <v>7029.829416395053</v>
+        <v>6935.589012973292</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>7306.380317092007</v>
+        <v>7136.226589233885</v>
       </c>
       <c r="J84" s="156" t="n">
-        <v>7741.305667019603</v>
+        <v>7659.25785341142</v>
       </c>
       <c r="K84" s="156" t="n">
-        <v>7949.174763829446</v>
+        <v>7950.538157852162</v>
       </c>
       <c r="L84" s="157" t="n">
-        <v>8271.766030274404</v>
+        <v>8355.610654626669</v>
       </c>
       <c r="M84" s="158" t="n">
-        <v>65327897.4562111</v>
+        <v>64452125.50695007</v>
       </c>
       <c r="N84" s="159" t="n">
-        <v>76564698.04524426</v>
+        <v>74781630.61248913</v>
       </c>
       <c r="O84" s="159" t="n">
-        <v>90556170.6565434</v>
+        <v>89596392.53503701</v>
       </c>
       <c r="P84" s="159" t="n">
-        <v>106558583.5274029</v>
+        <v>106576859.8064088</v>
       </c>
       <c r="Q84" s="160" t="n">
-        <v>127360406.7355469</v>
+        <v>128651362.6718017</v>
       </c>
       <c r="S84" s="32" t="inlineStr">
         <is>
@@ -8820,49 +8820,49 @@
         </is>
       </c>
       <c r="T84" s="155" t="n">
-        <v>4512.207364807332</v>
+        <v>4451.717669084367</v>
       </c>
       <c r="U84" s="156" t="n">
-        <v>4689.276414635216</v>
+        <v>4580.070784996582</v>
       </c>
       <c r="V84" s="156" t="n">
-        <v>4968.058014095451</v>
+        <v>4915.403033725443</v>
       </c>
       <c r="W84" s="156" t="n">
-        <v>5101.00628234837</v>
+        <v>5101.88117586648</v>
       </c>
       <c r="X84" s="157" t="n">
-        <v>5307.589215259919</v>
+        <v>5361.388225331149</v>
       </c>
       <c r="Y84" s="155" t="n">
-        <v>4509.074449068287</v>
+        <v>4448.626752549804</v>
       </c>
       <c r="Z84" s="156" t="n">
-        <v>4686.347390508336</v>
+        <v>4577.209973083211</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>4965.219565847234</v>
+        <v>4912.594669352327</v>
       </c>
       <c r="AB84" s="156" t="n">
-        <v>5098.429307585334</v>
+        <v>5099.303759116433</v>
       </c>
       <c r="AC84" s="157" t="n">
-        <v>5305.223747568379</v>
+        <v>5358.998780686044</v>
       </c>
       <c r="AD84" s="158" t="n">
-        <v>65327897.4562111</v>
+        <v>64452125.50695007</v>
       </c>
       <c r="AE84" s="159" t="n">
-        <v>76564698.04524426</v>
+        <v>74781630.61248913</v>
       </c>
       <c r="AF84" s="159" t="n">
-        <v>90556170.6565434</v>
+        <v>89596392.53503701</v>
       </c>
       <c r="AG84" s="159" t="n">
-        <v>106558583.5274029</v>
+        <v>106576859.8064088</v>
       </c>
       <c r="AH84" s="160" t="n">
-        <v>127360406.7355469</v>
+        <v>128651362.6718017</v>
       </c>
     </row>
     <row r="85" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -8872,49 +8872,49 @@
         </is>
       </c>
       <c r="C85" s="179" t="n">
-        <v>988.0627323636136</v>
+        <v>970.8875353216724</v>
       </c>
       <c r="D85" s="180" t="n">
-        <v>1070.46901103065</v>
+        <v>1039.363718162796</v>
       </c>
       <c r="E85" s="180" t="n">
-        <v>1160.060255096588</v>
+        <v>1125.691609071094</v>
       </c>
       <c r="F85" s="180" t="n">
-        <v>1241.399808343873</v>
+        <v>1203.661055621547</v>
       </c>
       <c r="G85" s="181" t="n">
-        <v>1320.952317649107</v>
+        <v>1280.557957562904</v>
       </c>
       <c r="H85" s="179" t="n">
-        <v>980.2752935322544</v>
+        <v>963.2354631952803</v>
       </c>
       <c r="I85" s="180" t="n">
-        <v>1064.169046593379</v>
+        <v>1033.246815763621</v>
       </c>
       <c r="J85" s="180" t="n">
-        <v>1155.415665668235</v>
+        <v>1121.184623055404</v>
       </c>
       <c r="K85" s="180" t="n">
-        <v>1238.709096626752</v>
+        <v>1201.052141970976</v>
       </c>
       <c r="L85" s="181" t="n">
-        <v>1320.455760182396</v>
+        <v>1280.076584687526</v>
       </c>
       <c r="M85" s="182" t="n">
-        <v>157083335.1345873</v>
+        <v>154352802.8064548</v>
       </c>
       <c r="N85" s="183" t="n">
-        <v>181696033.4346238</v>
+        <v>176416377.2515178</v>
       </c>
       <c r="O85" s="183" t="n">
-        <v>210130847.0883107</v>
+        <v>203905383.6514876</v>
       </c>
       <c r="P85" s="183" t="n">
-        <v>243452461.254995</v>
+        <v>236051467.4952158</v>
       </c>
       <c r="Q85" s="184" t="n">
-        <v>285869613.2857477</v>
+        <v>277127798.8065398</v>
       </c>
       <c r="S85" s="51" t="inlineStr">
         <is>
@@ -8922,49 +8922,49 @@
         </is>
       </c>
       <c r="T85" s="185" t="n">
-        <v>1114.092234885803</v>
+        <v>1094.726304939952</v>
       </c>
       <c r="U85" s="186" t="n">
-        <v>1205.060331151552</v>
+        <v>1170.04413344975</v>
       </c>
       <c r="V85" s="186" t="n">
-        <v>1303.69507527979</v>
+        <v>1265.071017287439</v>
       </c>
       <c r="W85" s="186" t="n">
-        <v>1391.204482554559</v>
+        <v>1348.911643776566</v>
       </c>
       <c r="X85" s="187" t="n">
-        <v>1477.347792803904</v>
+        <v>1432.170901921662</v>
       </c>
       <c r="Y85" s="185" t="n">
-        <v>1105.719237149672</v>
+        <v>1086.498852502959</v>
       </c>
       <c r="Z85" s="186" t="n">
-        <v>1198.299492903104</v>
+        <v>1163.479749140261</v>
       </c>
       <c r="AA85" s="186" t="n">
-        <v>1298.714690016696</v>
+        <v>1260.238183927297</v>
       </c>
       <c r="AB85" s="186" t="n">
-        <v>1388.313858028959</v>
+        <v>1346.108894698869</v>
       </c>
       <c r="AC85" s="187" t="n">
-        <v>1476.771853100728</v>
+        <v>1431.612574296868</v>
       </c>
       <c r="AD85" s="188" t="n">
-        <v>157083335.1345873</v>
+        <v>154352802.8064548</v>
       </c>
       <c r="AE85" s="189" t="n">
-        <v>181696033.4346238</v>
+        <v>176416377.2515178</v>
       </c>
       <c r="AF85" s="189" t="n">
-        <v>210130847.0883107</v>
+        <v>203905383.6514876</v>
       </c>
       <c r="AG85" s="189" t="n">
-        <v>243452461.254995</v>
+        <v>236051467.4952158</v>
       </c>
       <c r="AH85" s="190" t="n">
-        <v>285869613.2857477</v>
+        <v>277127798.8065398</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" thickBot="1"/>
@@ -9287,7 +9287,7 @@
         <v>123534.7071570992</v>
       </c>
       <c r="E90" s="75" t="n">
-        <v>131781.8177623025</v>
+        <v>131781.8177623026</v>
       </c>
       <c r="F90" s="75" t="n">
         <v>142072.9871695138</v>
@@ -9331,7 +9331,7 @@
         </is>
       </c>
       <c r="T90" s="74" t="n">
-        <v>94022.74165982254</v>
+        <v>94022.74165982255</v>
       </c>
       <c r="U90" s="75" t="n">
         <v>100671.4901834258</v>
@@ -9361,7 +9361,7 @@
         <v>30.16412813999912</v>
       </c>
       <c r="AD90" s="74" t="n">
-        <v>94816.92580116398</v>
+        <v>94816.92580116399</v>
       </c>
       <c r="AE90" s="75" t="n">
         <v>101302.3963567819</v>
@@ -9404,7 +9404,7 @@
         </is>
       </c>
       <c r="C91" s="79" t="n">
-        <v>25736.05101325882</v>
+        <v>25736.05101325883</v>
       </c>
       <c r="D91" s="80" t="n">
         <v>26483.14423816907</v>
@@ -9416,7 +9416,7 @@
         <v>29542.07912993147</v>
       </c>
       <c r="G91" s="81" t="n">
-        <v>32259.38220138617</v>
+        <v>32259.38220138618</v>
       </c>
       <c r="H91" s="79" t="n">
         <v>231.3841025303798</v>
@@ -9440,13 +9440,13 @@
         <v>26672.47541003757</v>
       </c>
       <c r="O91" s="80" t="n">
-        <v>27770.34595583852</v>
+        <v>27770.34595583853</v>
       </c>
       <c r="P91" s="80" t="n">
-        <v>29635.90281643001</v>
+        <v>29635.90281643002</v>
       </c>
       <c r="Q91" s="81" t="n">
-        <v>32294.10343555032</v>
+        <v>32294.10343555033</v>
       </c>
       <c r="S91" s="32" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>26179.60736526955</v>
       </c>
       <c r="V91" s="80" t="n">
-        <v>27309.07140925933</v>
+        <v>27309.07140925934</v>
       </c>
       <c r="W91" s="80" t="n">
         <v>29203.48223836126</v>
@@ -9484,13 +9484,13 @@
         <v>34.60226326579415</v>
       </c>
       <c r="AD91" s="79" t="n">
-        <v>25671.66823255158</v>
+        <v>25671.66823255159</v>
       </c>
       <c r="AE91" s="80" t="n">
-        <v>26368.28980156898</v>
+        <v>26368.28980156899</v>
       </c>
       <c r="AF91" s="80" t="n">
-        <v>27453.21801292077</v>
+        <v>27453.21801292078</v>
       </c>
       <c r="AG91" s="80" t="n">
         <v>29296.98444180949</v>
@@ -9530,7 +9530,7 @@
         <v>150017.8513952683</v>
       </c>
       <c r="E92" s="86" t="n">
-        <v>159407.5215038081</v>
+        <v>159407.5215038082</v>
       </c>
       <c r="F92" s="86" t="n">
         <v>171615.0662994452</v>
@@ -9560,7 +9560,7 @@
         <v>150990.2302680237</v>
       </c>
       <c r="O92" s="86" t="n">
-        <v>160118.3466929539</v>
+        <v>160118.346692954</v>
       </c>
       <c r="P92" s="86" t="n">
         <v>172031.9561052827</v>
@@ -9639,7 +9639,7 @@
         <v>8584.818806935771</v>
       </c>
       <c r="D93" s="80" t="n">
-        <v>9246.766475939343</v>
+        <v>9246.766475939345</v>
       </c>
       <c r="E93" s="80" t="n">
         <v>10041.54286424376</v>
@@ -9669,7 +9669,7 @@
         <v>8622.031676268572</v>
       </c>
       <c r="N93" s="80" t="n">
-        <v>9270.435732483327</v>
+        <v>9270.435732483329</v>
       </c>
       <c r="O93" s="80" t="n">
         <v>10049.88169191919</v>
@@ -9689,13 +9689,13 @@
         <v>7054.851945895035</v>
       </c>
       <c r="U93" s="80" t="n">
-        <v>7598.828808514154</v>
+        <v>7598.828808514156</v>
       </c>
       <c r="V93" s="80" t="n">
         <v>8251.961958517371</v>
       </c>
       <c r="W93" s="80" t="n">
-        <v>9122.023522871783</v>
+        <v>9122.023522871785</v>
       </c>
       <c r="X93" s="81" t="n">
         <v>10295.70244977662</v>
@@ -9719,13 +9719,13 @@
         <v>7087.706909349458</v>
       </c>
       <c r="AE93" s="80" t="n">
-        <v>7619.726217735445</v>
+        <v>7619.726217735447</v>
       </c>
       <c r="AF93" s="80" t="n">
         <v>8259.324246979435</v>
       </c>
       <c r="AG93" s="80" t="n">
-        <v>9122.023522871783</v>
+        <v>9122.023522871785</v>
       </c>
       <c r="AH93" s="81" t="n">
         <v>10295.70244977662</v>
@@ -9789,10 +9789,10 @@
         <v>150951.1467452348</v>
       </c>
       <c r="N94" s="86" t="n">
-        <v>160260.666000507</v>
+        <v>160260.6660005071</v>
       </c>
       <c r="O94" s="86" t="n">
-        <v>170168.2283848731</v>
+        <v>170168.2283848732</v>
       </c>
       <c r="P94" s="86" t="n">
         <v>183132.2484568503</v>
@@ -9815,7 +9815,7 @@
         <v>142953.2980884953</v>
       </c>
       <c r="W94" s="86" t="n">
-        <v>154104.2991247606</v>
+        <v>154104.2991247607</v>
       </c>
       <c r="X94" s="87" t="n">
         <v>169506.0006699097</v>
@@ -9839,7 +9839,7 @@
         <v>127576.300943065</v>
       </c>
       <c r="AE94" s="86" t="n">
-        <v>135290.4123760863</v>
+        <v>135290.4123760864</v>
       </c>
       <c r="AF94" s="86" t="n">
         <v>143560.9839589229</v>
@@ -9994,7 +9994,7 @@
         <v>169734.9774373071</v>
       </c>
       <c r="E96" s="133" t="n">
-        <v>181137.8729381732</v>
+        <v>181137.8729381733</v>
       </c>
       <c r="F96" s="133" t="n">
         <v>196111.2444344421</v>
@@ -10024,7 +10024,7 @@
         <v>170739.8218509265</v>
       </c>
       <c r="O96" s="133" t="n">
-        <v>181866.0187256345</v>
+        <v>181866.0187256346</v>
       </c>
       <c r="P96" s="133" t="n">
         <v>196537.2353508696</v>
@@ -10041,7 +10041,7 @@
         <v>140996.7058523558</v>
       </c>
       <c r="U96" s="136" t="n">
-        <v>150777.5409559749</v>
+        <v>150777.540955975</v>
       </c>
       <c r="V96" s="136" t="n">
         <v>161180.9778779857</v>
@@ -10077,10 +10077,10 @@
         <v>161799.0838970253</v>
       </c>
       <c r="AG96" s="136" t="n">
-        <v>175358.3743668982</v>
+        <v>175358.3743668983</v>
       </c>
       <c r="AH96" s="137" t="n">
-        <v>193577.3712679565</v>
+        <v>193577.3712679566</v>
       </c>
       <c r="AJ96" s="138" t="n"/>
       <c r="AK96" s="139" t="n"/>
